--- a/Vascano Tequila - RFP Creative Services 2022 (8) - Scenarios A & B - Workfront Export.xlsx
+++ b/Vascano Tequila - RFP Creative Services 2022 (8) - Scenarios A & B - Workfront Export.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O53"/>
+  <dimension ref="A1:O58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,11 +567,7 @@
           <t>Development</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Deliverable</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -610,7 +606,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -620,32 +616,20 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Business Analyst</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Mid</t>
-        </is>
-      </c>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>35</v>
+        <v>227</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -663,17 +647,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.1.2</t>
+          <t>1.1.1.1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.1.1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>design_prod</t>
+          <t>research</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -683,17 +667,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>design_prod</t>
+          <t>research</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>UI Designer</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -702,13 +686,13 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
         <v>3</v>
-      </c>
-      <c r="L5" t="n">
-        <v>7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -726,17 +710,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.1.3</t>
+          <t>1.1.1.2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.1.1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>design_prod</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -746,17 +730,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>design_prod</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>UI Designer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -765,17 +749,17 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1.1.2</t>
+          <t>1.1.1.1</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -789,17 +773,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.1.4</t>
+          <t>1.1.1.3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.1.1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>qa</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -809,17 +793,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>qa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Frontend Engineer</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -828,17 +812,17 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="K7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L7" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1.1.3</t>
+          <t>1.1.1.2</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -852,52 +836,60 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1.1.4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1.1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Post-Production</t>
+          <t>development</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Post-Production</t>
+          <t>Development</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Deliverable</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Frontend Engineer</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
+      </c>
       <c r="J8" t="n">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="K8" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="L8" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.1.1.3</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Core/T2_MediumVolume</t>
-        </is>
-      </c>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -907,17 +899,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.2.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>Post-Production</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -925,42 +917,30 @@
           <t>Post-Production</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Producer</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Mid</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>188</v>
       </c>
       <c r="K9" t="n">
         <v>22</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Core/T2_MediumVolume</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -970,7 +950,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -980,7 +960,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -990,36 +970,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>prepro_docs</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Copywriter</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Mid</t>
-        </is>
-      </c>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>188</v>
       </c>
       <c r="K10" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L10" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1.2.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1033,17 +1001,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.2.3</t>
+          <t>1.2.1.1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>edit</t>
+          <t>research</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1053,17 +1021,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>edit</t>
+          <t>research</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Editor</t>
+          <t>Producer</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1072,17 +1040,17 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="L11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1096,17 +1064,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.2.4</t>
+          <t>1.2.1.2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>motion</t>
+          <t>prepro_docs</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1116,17 +1084,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>motion</t>
+          <t>prepro_docs</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Editor</t>
+          <t>Copywriter</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1135,17 +1103,17 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="L12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1.2.3</t>
+          <t>1.2.1.1</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1159,17 +1127,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.2.5</t>
+          <t>1.2.1.3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>edit</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1179,17 +1147,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>edit</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Colorist</t>
+          <t>Editor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1198,17 +1166,17 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="K13" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1.2.4</t>
+          <t>1.2.1.2</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1222,17 +1190,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.2.6</t>
+          <t>1.2.1.4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>retouch</t>
+          <t>motion</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1242,17 +1210,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>retouch</t>
+          <t>motion</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Retoucher</t>
+          <t>Editor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1261,17 +1229,17 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="K14" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1.2.5</t>
+          <t>1.2.1.3</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1285,17 +1253,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.2.7</t>
+          <t>1.2.1.5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>sound</t>
+          <t>color</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1305,17 +1273,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>sound</t>
+          <t>color</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sound Designer</t>
+          <t>Colorist</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1324,17 +1292,17 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="K15" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1.2.6</t>
+          <t>1.2.1.4</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1348,17 +1316,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.2.8</t>
+          <t>1.2.1.6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>retouch</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1368,17 +1336,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>retouch</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>QA Specialist</t>
+          <t>Retoucher</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1387,17 +1355,17 @@
         </is>
       </c>
       <c r="J16" t="n">
+        <v>8</v>
+      </c>
+      <c r="K16" t="n">
+        <v>43</v>
+      </c>
+      <c r="L16" t="n">
         <v>3</v>
       </c>
-      <c r="K16" t="n">
-        <v>48</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1.2.7</t>
+          <t>1.2.1.5</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1411,17 +1379,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.2.9</t>
+          <t>1.2.1.7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>analytics_tagging</t>
+          <t>sound</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1431,17 +1399,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>analytics_tagging</t>
+          <t>sound</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Sound Designer</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1450,17 +1418,17 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K17" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1.2.8</t>
+          <t>1.2.1.6</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1474,17 +1442,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.2.10</t>
+          <t>1.2.1.8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>qa</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1494,17 +1462,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>qa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Producer</t>
+          <t>QA Specialist</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1513,17 +1481,17 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1.2.9</t>
+          <t>1.2.1.7</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1537,17 +1505,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.2.11</t>
+          <t>1.2.1.9</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>analytics_tagging</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1557,17 +1525,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>analytics_tagging</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Account Manager</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1576,17 +1544,17 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="L19" t="n">
         <v>3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1.2.10</t>
+          <t>1.2.1.8</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -1600,17 +1568,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.2.12</t>
+          <t>1.2.1.10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>library</t>
+          <t>internal_review</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1620,17 +1588,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>library</t>
+          <t>internal_review</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Editor</t>
+          <t>Producer</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1639,17 +1607,17 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K20" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="L20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1.2.11</t>
+          <t>1.2.1.9</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -1663,17 +1631,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.2.13</t>
+          <t>1.2.1.11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>notes_triage</t>
+          <t>client_review</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1683,17 +1651,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>notes_triage</t>
+          <t>client_review</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Account Manager</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1702,17 +1670,17 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="K21" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1.2.12</t>
+          <t>1.2.1.10</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -1726,17 +1694,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.2.14</t>
+          <t>1.2.1.12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>library</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1746,12 +1714,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>library</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1765,17 +1733,17 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="K22" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1.2.13</t>
+          <t>1.2.1.11</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -1789,52 +1757,60 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2.1.13</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Pre-Production</t>
+          <t>notes_triage</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pre-Production</t>
+          <t>Post-Production</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Deliverable</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>notes_triage</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
+      </c>
       <c r="J23" t="n">
-        <v>396</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L23" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.2.1.12</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Core/T2_MediumVolume</t>
-        </is>
-      </c>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1844,56 +1820,56 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.3.1</t>
+          <t>1.2.1.14</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>brief</t>
+          <t>general</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pre-Production</t>
+          <t>Post-Production</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>brief</t>
+          <t>general</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Art Director</t>
+          <t>Editor</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Lead/Director</t>
+          <t>Mid</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="K24" t="n">
         <v>63</v>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2.1.13</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -1907,17 +1883,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.3.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>deck_build</t>
+          <t>Pre-Production</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1925,42 +1901,30 @@
           <t>Pre-Production</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>deck_build</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Strategist</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Mid</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>20</v>
+        <v>396</v>
       </c>
       <c r="K25" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="L25" t="n">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1.3.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Core/T2_MediumVolume</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1970,7 +1934,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.3.3</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1980,7 +1944,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>design_prod</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1990,36 +1954,24 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>design_prod</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Media Manager / DIT</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Mid</t>
-        </is>
-      </c>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>396</v>
       </c>
       <c r="K26" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="L26" t="n">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1.3.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -2033,17 +1985,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.3.4</t>
+          <t>1.3.1.1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>brief</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2053,36 +2005,36 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>brief</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Producer</t>
+          <t>Art Director</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Mid</t>
+          <t>Lead/Director</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>130</v>
+        <v>2</v>
       </c>
       <c r="K27" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="L27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1.3.3</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -2096,17 +2048,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.3.5</t>
+          <t>1.3.1.2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>prepro_coord</t>
+          <t>deck_build</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2116,17 +2068,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>prepro_coord</t>
+          <t>deck_build</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Producer</t>
+          <t>Strategist</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2135,17 +2087,17 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="K28" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="L28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1.3.4</t>
+          <t>1.3.1.1</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -2159,17 +2111,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.3.6</t>
+          <t>1.3.1.3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>edit</t>
+          <t>design_prod</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2179,17 +2131,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>edit</t>
+          <t>design_prod</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Editor</t>
+          <t>Media Manager / DIT</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2198,17 +2150,17 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K29" t="n">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="L29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1.3.5</t>
+          <t>1.3.1.2</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -2222,17 +2174,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.3.7</t>
+          <t>1.3.1.4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>prepro_docs</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2242,17 +2194,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>prepro_docs</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>QA Specialist</t>
+          <t>Producer</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2261,17 +2213,17 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>3</v>
+        <v>130</v>
       </c>
       <c r="K30" t="n">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1.3.6</t>
+          <t>1.3.1.3</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -2285,17 +2237,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.3.8</t>
+          <t>1.3.1.5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>prepro_coord</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2305,17 +2257,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>prepro_coord</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Designer</t>
+          <t>Producer</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2324,17 +2276,17 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="K31" t="n">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="L31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1.3.7</t>
+          <t>1.3.1.4</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -2348,17 +2300,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.3.9</t>
+          <t>1.3.1.6</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>analytics_tagging</t>
+          <t>edit</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2368,17 +2320,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>analytics_tagging</t>
+          <t>edit</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Producer</t>
+          <t>Editor</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2387,17 +2339,17 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K32" t="n">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="L32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1.3.8</t>
+          <t>1.3.1.5</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -2411,17 +2363,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.3.10</t>
+          <t>1.3.1.7</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>community_mgmt</t>
+          <t>qa</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2431,17 +2383,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>community_mgmt</t>
+          <t>qa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Designer</t>
+          <t>QA Specialist</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2450,17 +2402,17 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K33" t="n">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="L33" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1.3.9</t>
+          <t>1.3.1.6</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -2474,17 +2426,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.3.11</t>
+          <t>1.3.1.8</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>development</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2494,17 +2446,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>development</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Producer</t>
+          <t>Designer</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2513,17 +2465,17 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K34" t="n">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="L34" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1.3.10</t>
+          <t>1.3.1.7</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -2537,17 +2489,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.3.12</t>
+          <t>1.3.1.9</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>analytics_tagging</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2557,17 +2509,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>analytics_tagging</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Account Manager</t>
+          <t>Producer</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2576,17 +2528,17 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="K35" t="n">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="L35" t="n">
         <v>3</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1.3.11</t>
+          <t>1.3.1.8</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -2600,17 +2552,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.3.13</t>
+          <t>1.3.1.10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>status_meeting</t>
+          <t>community_mgmt</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2620,36 +2572,36 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>status_meeting</t>
+          <t>community_mgmt</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Creative Director</t>
+          <t>Designer</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Lead/Director</t>
+          <t>Mid</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K36" t="n">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="L36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1.3.12</t>
+          <t>1.3.1.9</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -2663,17 +2615,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.3.14</t>
+          <t>1.3.1.11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>internal_review</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2683,17 +2635,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>internal_review</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Designer</t>
+          <t>Producer</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2702,17 +2654,17 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="K37" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.3.13</t>
+          <t>1.3.1.10</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -2726,17 +2678,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.3.15</t>
+          <t>1.3.1.12</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>client_review</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2746,17 +2698,17 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>client_review</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Designer</t>
+          <t>Account Manager</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2765,17 +2717,17 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="K38" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1.3.14</t>
+          <t>1.3.1.11</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -2789,52 +2741,60 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.3.1.13</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Brand Identity Development</t>
+          <t>status_meeting</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Brand Identity Development</t>
+          <t>Pre-Production</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Deliverable</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>status_meeting</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Creative Director</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Lead/Director</t>
+        </is>
+      </c>
       <c r="J39" t="n">
-        <v>255</v>
+        <v>2</v>
       </c>
       <c r="K39" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L39" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3.1.12</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Core/T2_MediumVolume</t>
-        </is>
-      </c>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2844,32 +2804,32 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.4.1</t>
+          <t>1.3.1.14</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>general</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Brand Identity Development</t>
+          <t>Pre-Production</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>general</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2883,17 +2843,17 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="K40" t="n">
         <v>120</v>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.3.1.13</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -2907,37 +2867,37 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.4.2</t>
+          <t>1.3.1.15</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>retouch</t>
+          <t>style_guide</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Brand Identity Development</t>
+          <t>Pre-Production</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>retouch</t>
+          <t>style_guide</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Retoucher</t>
+          <t>Designer</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2946,17 +2906,17 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K41" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="L41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1.4.1</t>
+          <t>1.3.1.14</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -2970,17 +2930,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.4.3</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Brand Identity Development</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2988,42 +2948,30 @@
           <t>Brand Identity Development</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>qa</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>QA Specialist</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Mid</t>
-        </is>
-      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
-        <v>5</v>
+        <v>255</v>
       </c>
       <c r="K42" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1.4.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Core/T2_MediumVolume</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3033,7 +2981,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.4.4</t>
+          <t>1.4.1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3043,7 +2991,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3053,36 +3001,24 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>internal_review</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Art Director</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Lead/Director</t>
-        </is>
-      </c>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
+        <v>255</v>
+      </c>
+      <c r="K43" t="n">
+        <v>120</v>
+      </c>
+      <c r="L43" t="n">
         <v>12</v>
       </c>
-      <c r="K43" t="n">
-        <v>127</v>
-      </c>
-      <c r="L43" t="n">
-        <v>2</v>
-      </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1.4.3</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -3096,17 +3032,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.4.5</t>
+          <t>1.4.1.1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.4.1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>color</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3116,17 +3052,17 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>color</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Account Manager</t>
+          <t>Designer</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3135,17 +3071,17 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="K44" t="n">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="L44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1.4.4</t>
+          <t>1.4.1</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -3159,17 +3095,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.4.6</t>
+          <t>1.4.1.2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.4.1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>retouch</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3179,17 +3115,17 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>retouch</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Designer</t>
+          <t>Retoucher</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3198,17 +3134,17 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>187</v>
+        <v>4</v>
       </c>
       <c r="K45" t="n">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>1.4.5</t>
+          <t>1.4.1.1</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -3222,52 +3158,60 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4.1.3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.4.1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Brand Style &amp; Usage Guidelines</t>
+          <t>qa</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Brand Style &amp; Usage Guidelines</t>
+          <t>Brand Identity Development</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Deliverable</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>qa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>QA Specialist</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
+      </c>
       <c r="J46" t="n">
-        <v>250</v>
+        <v>5</v>
       </c>
       <c r="K46" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="L46" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.4.1.2</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>Core/T2_MediumVolume</t>
-        </is>
-      </c>
+      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3277,56 +3221,56 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.5.1</t>
+          <t>1.4.1.4</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4.1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>internal_review</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Brand Style &amp; Usage Guidelines</t>
+          <t>Brand Identity Development</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>internal_review</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Designer</t>
+          <t>Art Director</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Mid</t>
+          <t>Lead/Director</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K47" t="n">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="L47" t="n">
         <v>2</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4.1.3</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -3340,37 +3284,37 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1.5.2</t>
+          <t>1.4.1.5</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4.1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>client_review</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Brand Style &amp; Usage Guidelines</t>
+          <t>Brand Identity Development</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>client_review</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>QA Specialist</t>
+          <t>Account Manager</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3379,17 +3323,17 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="K48" t="n">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="L48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>1.5.1</t>
+          <t>1.4.1.4</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -3403,56 +3347,56 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1.5.3</t>
+          <t>1.4.1.6</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4.1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>brand_identity</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Brand Style &amp; Usage Guidelines</t>
+          <t>Brand Identity Development</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>brand_identity</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Art Director</t>
+          <t>Designer</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Lead/Director</t>
+          <t>Mid</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>12</v>
+        <v>187</v>
       </c>
       <c r="K49" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>1.5.2</t>
+          <t>1.4.1.5</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -3466,17 +3410,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1.5.4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Brand Style &amp; Usage Guidelines</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3484,42 +3428,30 @@
           <t>Brand Style &amp; Usage Guidelines</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>client_review</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Account Manager</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Mid</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
-        <v>31</v>
+        <v>250</v>
       </c>
       <c r="K50" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="L50" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>1.5.3</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Core/T2_MediumVolume</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3529,7 +3461,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1.5.5</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3539,7 +3471,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3549,36 +3481,24 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>brand_identity</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Designer</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Mid</t>
-        </is>
-      </c>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
-        <v>55</v>
+        <v>250</v>
       </c>
       <c r="K51" t="n">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>1.5.4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -3592,17 +3512,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1.5.6</t>
+          <t>1.5.1.1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>color</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3612,12 +3532,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>color</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3631,17 +3551,17 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>119</v>
+        <v>13</v>
       </c>
       <c r="K52" t="n">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>1.5.5</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -3655,17 +3575,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1.5.7</t>
+          <t>1.5.1.2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>treatment</t>
+          <t>qa</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3675,40 +3595,355 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>treatment</t>
+          <t>qa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Creative Director</t>
+          <t>QA Specialist</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Lead/Director</t>
+          <t>Mid</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K53" t="n">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>1.5.6</t>
+          <t>1.5.1.1</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Vascano Tequila - RFP Creative Services 2022 (8)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1.5.1.3</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1.5.1</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>internal_review</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Brand Style &amp; Usage Guidelines</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>internal_review</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Art Director</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Lead/Director</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>12</v>
+      </c>
+      <c r="K54" t="n">
+        <v>136</v>
+      </c>
+      <c r="L54" t="n">
+        <v>2</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>1.5.1.2</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Vascano Tequila - RFP Creative Services 2022 (8)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1.5.1.4</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1.5.1</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>client_review</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Brand Style &amp; Usage Guidelines</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>client_review</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Account Manager</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>31</v>
+      </c>
+      <c r="K55" t="n">
+        <v>138</v>
+      </c>
+      <c r="L55" t="n">
+        <v>3</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>1.5.1.3</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Vascano Tequila - RFP Creative Services 2022 (8)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1.5.1.5</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1.5.1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>brand_identity</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Brand Style &amp; Usage Guidelines</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>brand_identity</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Designer</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>55</v>
+      </c>
+      <c r="K56" t="n">
+        <v>141</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>1.5.1.4</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Vascano Tequila - RFP Creative Services 2022 (8)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1.5.1.6</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1.5.1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>style_guide</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Brand Style &amp; Usage Guidelines</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>style_guide</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Designer</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>119</v>
+      </c>
+      <c r="K57" t="n">
+        <v>141</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>1.5.1.5</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Vascano Tequila - RFP Creative Services 2022 (8)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1.5.1.7</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1.5.1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>treatment</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Brand Style &amp; Usage Guidelines</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>treatment</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Creative Director</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Lead/Director</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>15</v>
+      </c>
+      <c r="K58" t="n">
+        <v>141</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>1.5.1.6</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3721,7 +3956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O53"/>
+  <dimension ref="A1:O58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3862,11 +4097,7 @@
           <t>Development</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Deliverable</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -3905,7 +4136,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3915,32 +4146,20 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Business Analyst</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Mid</t>
-        </is>
-      </c>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>55</v>
+        <v>348</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -3958,17 +4177,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.1.2</t>
+          <t>1.1.1.1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.1.1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>design_prod</t>
+          <t>research</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3978,17 +4197,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>design_prod</t>
+          <t>research</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>UI Designer</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -3997,13 +4216,13 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
         <v>4</v>
-      </c>
-      <c r="L5" t="n">
-        <v>9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -4021,17 +4240,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.1.3</t>
+          <t>1.1.1.2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.1.1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>design_prod</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4041,17 +4260,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>design_prod</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>UI Designer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -4060,17 +4279,17 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="K6" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1.1.2</t>
+          <t>1.1.1.1</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -4084,17 +4303,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.1.4</t>
+          <t>1.1.1.3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.1.1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>qa</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -4104,17 +4323,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>qa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Frontend Engineer</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -4123,17 +4342,17 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>217</v>
+        <v>66</v>
       </c>
       <c r="K7" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L7" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1.1.3</t>
+          <t>1.1.1.2</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -4147,52 +4366,60 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1.1.4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.1.1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Post-Production</t>
+          <t>development</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Post-Production</t>
+          <t>Development</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Deliverable</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Frontend Engineer</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
+      </c>
       <c r="J8" t="n">
-        <v>288</v>
+        <v>217</v>
       </c>
       <c r="K8" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="L8" t="n">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.1.1.3</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Advanced/T1_LargeVolume</t>
-        </is>
-      </c>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4202,17 +4429,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.2.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>Post-Production</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4220,42 +4447,30 @@
           <t>Post-Production</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Producer</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Mid</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>288</v>
       </c>
       <c r="K9" t="n">
         <v>28</v>
       </c>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Advanced/T1_LargeVolume</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4265,7 +4480,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4275,7 +4490,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4285,36 +4500,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>prepro_docs</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Copywriter</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Mid</t>
-        </is>
-      </c>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>288</v>
       </c>
       <c r="K10" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1.2.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -4328,17 +4531,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.2.3</t>
+          <t>1.2.1.1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>edit</t>
+          <t>research</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4348,17 +4551,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>edit</t>
+          <t>research</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Editor</t>
+          <t>Producer</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4367,17 +4570,17 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="L11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -4391,17 +4594,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.2.4</t>
+          <t>1.2.1.2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>motion</t>
+          <t>prepro_docs</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -4411,17 +4614,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>motion</t>
+          <t>prepro_docs</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Editor</t>
+          <t>Copywriter</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -4430,17 +4633,17 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1.2.3</t>
+          <t>1.2.1.1</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -4454,17 +4657,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.2.5</t>
+          <t>1.2.1.3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>edit</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -4474,17 +4677,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>edit</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Colorist</t>
+          <t>Editor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -4493,17 +4696,17 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="K13" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="L13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1.2.4</t>
+          <t>1.2.1.2</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -4517,17 +4720,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.2.6</t>
+          <t>1.2.1.4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>retouch</t>
+          <t>motion</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -4537,17 +4740,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>retouch</t>
+          <t>motion</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Retoucher</t>
+          <t>Editor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -4556,17 +4759,17 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="K14" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="L14" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1.2.5</t>
+          <t>1.2.1.3</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -4580,17 +4783,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.2.7</t>
+          <t>1.2.1.5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>sound</t>
+          <t>color</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -4600,17 +4803,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>sound</t>
+          <t>color</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sound Designer</t>
+          <t>Colorist</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -4619,17 +4822,17 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="K15" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="L15" t="n">
         <v>3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1.2.6</t>
+          <t>1.2.1.4</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -4643,17 +4846,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.2.8</t>
+          <t>1.2.1.6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>retouch</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -4663,17 +4866,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>retouch</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>QA Specialist</t>
+          <t>Retoucher</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4682,17 +4885,17 @@
         </is>
       </c>
       <c r="J16" t="n">
+        <v>13</v>
+      </c>
+      <c r="K16" t="n">
+        <v>55</v>
+      </c>
+      <c r="L16" t="n">
         <v>4</v>
       </c>
-      <c r="K16" t="n">
-        <v>62</v>
-      </c>
-      <c r="L16" t="n">
-        <v>3</v>
-      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1.2.7</t>
+          <t>1.2.1.5</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -4706,17 +4909,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.2.9</t>
+          <t>1.2.1.7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>analytics_tagging</t>
+          <t>sound</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -4726,17 +4929,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>analytics_tagging</t>
+          <t>sound</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Sound Designer</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -4745,17 +4948,17 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="K17" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="L17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1.2.8</t>
+          <t>1.2.1.6</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -4769,17 +4972,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.2.10</t>
+          <t>1.2.1.8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>qa</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -4789,17 +4992,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>qa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Producer</t>
+          <t>QA Specialist</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4808,17 +5011,17 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1.2.9</t>
+          <t>1.2.1.7</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -4832,17 +5035,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.2.11</t>
+          <t>1.2.1.9</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>analytics_tagging</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -4852,17 +5055,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>analytics_tagging</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Account Manager</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4871,17 +5074,17 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="L19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1.2.10</t>
+          <t>1.2.1.8</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -4895,17 +5098,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.2.12</t>
+          <t>1.2.1.10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>library</t>
+          <t>internal_review</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -4915,17 +5118,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>library</t>
+          <t>internal_review</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Editor</t>
+          <t>Producer</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -4934,17 +5137,17 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K20" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="L20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1.2.11</t>
+          <t>1.2.1.9</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -4958,17 +5161,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.2.13</t>
+          <t>1.2.1.11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>notes_triage</t>
+          <t>client_review</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -4978,17 +5181,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>notes_triage</t>
+          <t>client_review</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Account Manager</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -4997,17 +5200,17 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="K21" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1.2.12</t>
+          <t>1.2.1.10</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -5021,17 +5224,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.2.14</t>
+          <t>1.2.1.12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>library</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -5041,12 +5244,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>library</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -5060,17 +5263,17 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="K22" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1.2.13</t>
+          <t>1.2.1.11</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -5084,52 +5287,60 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2.1.13</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Pre-Production</t>
+          <t>notes_triage</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pre-Production</t>
+          <t>Post-Production</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Deliverable</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>notes_triage</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
+      </c>
       <c r="J23" t="n">
-        <v>606</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L23" t="n">
-        <v>69</v>
+        <v>2</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.2.1.12</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Advanced/T1_LargeVolume</t>
-        </is>
-      </c>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5139,56 +5350,56 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.3.1</t>
+          <t>1.2.1.14</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>brief</t>
+          <t>general</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pre-Production</t>
+          <t>Post-Production</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>brief</t>
+          <t>general</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Art Director</t>
+          <t>Editor</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Lead/Director</t>
+          <t>Mid</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="K24" t="n">
         <v>79</v>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2.1.13</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -5202,17 +5413,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.3.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>deck_build</t>
+          <t>Pre-Production</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -5220,42 +5431,30 @@
           <t>Pre-Production</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>deck_build</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Strategist</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Mid</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>31</v>
+        <v>606</v>
       </c>
       <c r="K25" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L25" t="n">
-        <v>6</v>
+        <v>69</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1.3.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Advanced/T1_LargeVolume</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5265,7 +5464,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.3.3</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -5275,7 +5474,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>design_prod</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -5285,36 +5484,24 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>design_prod</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Media Manager / DIT</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Mid</t>
-        </is>
-      </c>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>4</v>
+        <v>606</v>
       </c>
       <c r="K26" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="L26" t="n">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1.3.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -5328,17 +5515,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.3.4</t>
+          <t>1.3.1.1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>brief</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -5348,36 +5535,36 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>brief</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Producer</t>
+          <t>Art Director</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Mid</t>
+          <t>Lead/Director</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>199</v>
+        <v>4</v>
       </c>
       <c r="K27" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="L27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1.3.3</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -5391,17 +5578,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.3.5</t>
+          <t>1.3.1.2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>prepro_coord</t>
+          <t>deck_build</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -5411,17 +5598,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>prepro_coord</t>
+          <t>deck_build</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Producer</t>
+          <t>Strategist</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -5430,17 +5617,17 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>96</v>
+        <v>31</v>
       </c>
       <c r="K28" t="n">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="L28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1.3.4</t>
+          <t>1.3.1.1</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -5454,17 +5641,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.3.6</t>
+          <t>1.3.1.3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>edit</t>
+          <t>design_prod</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -5474,17 +5661,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>edit</t>
+          <t>design_prod</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Editor</t>
+          <t>Media Manager / DIT</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -5493,17 +5680,17 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="K29" t="n">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="L29" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1.3.5</t>
+          <t>1.3.1.2</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -5517,17 +5704,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.3.7</t>
+          <t>1.3.1.4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>prepro_docs</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -5537,17 +5724,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>prepro_docs</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>QA Specialist</t>
+          <t>Producer</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -5556,17 +5743,17 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>4</v>
+        <v>199</v>
       </c>
       <c r="K30" t="n">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="L30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1.3.6</t>
+          <t>1.3.1.3</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -5580,17 +5767,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.3.8</t>
+          <t>1.3.1.5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>prepro_coord</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -5600,17 +5787,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>prepro_coord</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Designer</t>
+          <t>Producer</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -5619,17 +5806,17 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="K31" t="n">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="L31" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1.3.7</t>
+          <t>1.3.1.4</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -5643,17 +5830,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.3.9</t>
+          <t>1.3.1.6</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>analytics_tagging</t>
+          <t>edit</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -5663,17 +5850,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>analytics_tagging</t>
+          <t>edit</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Producer</t>
+          <t>Editor</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -5682,17 +5869,17 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K32" t="n">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="L32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1.3.8</t>
+          <t>1.3.1.5</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -5706,17 +5893,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.3.10</t>
+          <t>1.3.1.7</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>community_mgmt</t>
+          <t>qa</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -5726,17 +5913,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>community_mgmt</t>
+          <t>qa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Designer</t>
+          <t>QA Specialist</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -5745,17 +5932,17 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K33" t="n">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="L33" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1.3.9</t>
+          <t>1.3.1.6</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -5769,17 +5956,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.3.11</t>
+          <t>1.3.1.8</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>development</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -5789,17 +5976,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>development</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Producer</t>
+          <t>Designer</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -5808,17 +5995,17 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="K34" t="n">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="L34" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1.3.10</t>
+          <t>1.3.1.7</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -5832,17 +6019,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.3.12</t>
+          <t>1.3.1.9</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>analytics_tagging</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -5852,17 +6039,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>analytics_tagging</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Account Manager</t>
+          <t>Producer</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -5871,17 +6058,17 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="K35" t="n">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1.3.11</t>
+          <t>1.3.1.8</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -5895,17 +6082,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.3.13</t>
+          <t>1.3.1.10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>status_meeting</t>
+          <t>community_mgmt</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -5915,36 +6102,36 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>status_meeting</t>
+          <t>community_mgmt</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Creative Director</t>
+          <t>Designer</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Lead/Director</t>
+          <t>Mid</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="K36" t="n">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="L36" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1.3.12</t>
+          <t>1.3.1.9</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -5958,17 +6145,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.3.14</t>
+          <t>1.3.1.11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>internal_review</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -5978,17 +6165,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>internal_review</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Designer</t>
+          <t>Producer</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -5997,17 +6184,17 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>118</v>
+        <v>27</v>
       </c>
       <c r="K37" t="n">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.3.13</t>
+          <t>1.3.1.10</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -6021,17 +6208,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.3.15</t>
+          <t>1.3.1.12</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>client_review</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -6041,17 +6228,17 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>client_review</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Designer</t>
+          <t>Account Manager</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -6060,17 +6247,17 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="K38" t="n">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1.3.14</t>
+          <t>1.3.1.11</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -6084,52 +6271,60 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.3.1.13</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Brand Identity Development</t>
+          <t>status_meeting</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Brand Identity Development</t>
+          <t>Pre-Production</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Deliverable</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>status_meeting</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Creative Director</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Lead/Director</t>
+        </is>
+      </c>
       <c r="J39" t="n">
-        <v>391</v>
+        <v>4</v>
       </c>
       <c r="K39" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="L39" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3.1.12</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Advanced/T1_LargeVolume</t>
-        </is>
-      </c>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6139,32 +6334,32 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.4.1</t>
+          <t>1.3.1.14</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>general</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Brand Identity Development</t>
+          <t>Pre-Production</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>general</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6178,17 +6373,17 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>23</v>
+        <v>118</v>
       </c>
       <c r="K40" t="n">
         <v>148</v>
       </c>
       <c r="L40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.3.1.13</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -6202,37 +6397,37 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.4.2</t>
+          <t>1.3.1.15</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>retouch</t>
+          <t>style_guide</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Brand Identity Development</t>
+          <t>Pre-Production</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>retouch</t>
+          <t>style_guide</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Retoucher</t>
+          <t>Designer</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -6241,17 +6436,17 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="K41" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1.4.1</t>
+          <t>1.3.1.14</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -6265,17 +6460,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.4.3</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Brand Identity Development</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -6283,42 +6478,30 @@
           <t>Brand Identity Development</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>qa</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>QA Specialist</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Mid</t>
-        </is>
-      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
-        <v>8</v>
+        <v>391</v>
       </c>
       <c r="K42" t="n">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="L42" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1.4.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Advanced/T1_LargeVolume</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6328,7 +6511,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.4.4</t>
+          <t>1.4.1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6338,7 +6521,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -6348,36 +6531,24 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>internal_review</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Art Director</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Lead/Director</t>
-        </is>
-      </c>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
-        <v>18</v>
+        <v>391</v>
       </c>
       <c r="K43" t="n">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="L43" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1.4.3</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -6391,17 +6562,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.4.5</t>
+          <t>1.4.1.1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.4.1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>color</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -6411,17 +6582,17 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>color</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Account Manager</t>
+          <t>Designer</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -6430,17 +6601,17 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="K44" t="n">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="L44" t="n">
         <v>3</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1.4.4</t>
+          <t>1.4.1</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -6454,17 +6625,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.4.6</t>
+          <t>1.4.1.2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.4.1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>retouch</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -6474,17 +6645,17 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>retouch</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Designer</t>
+          <t>Retoucher</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -6493,17 +6664,17 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>286</v>
+        <v>7</v>
       </c>
       <c r="K45" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>1.4.5</t>
+          <t>1.4.1.1</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -6517,52 +6688,60 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4.1.3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.4.1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Brand Style &amp; Usage Guidelines</t>
+          <t>qa</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Brand Style &amp; Usage Guidelines</t>
+          <t>Brand Identity Development</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Deliverable</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>qa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>QA Specialist</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
+      </c>
       <c r="J46" t="n">
-        <v>382</v>
+        <v>8</v>
       </c>
       <c r="K46" t="n">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="L46" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.4.1.2</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>Advanced/T1_LargeVolume</t>
-        </is>
-      </c>
+      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6572,56 +6751,56 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.5.1</t>
+          <t>1.4.1.4</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4.1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>internal_review</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Brand Style &amp; Usage Guidelines</t>
+          <t>Brand Identity Development</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>internal_review</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Designer</t>
+          <t>Art Director</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Mid</t>
+          <t>Lead/Director</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K47" t="n">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4.1.3</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -6635,37 +6814,37 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1.5.2</t>
+          <t>1.4.1.5</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4.1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>client_review</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Brand Style &amp; Usage Guidelines</t>
+          <t>Brand Identity Development</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>client_review</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>QA Specialist</t>
+          <t>Account Manager</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -6674,17 +6853,17 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="K48" t="n">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="L48" t="n">
         <v>3</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>1.5.1</t>
+          <t>1.4.1.4</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -6698,56 +6877,56 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1.5.3</t>
+          <t>1.4.1.6</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4.1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>brand_identity</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Brand Style &amp; Usage Guidelines</t>
+          <t>Brand Identity Development</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>brand_identity</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Art Director</t>
+          <t>Designer</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Lead/Director</t>
+          <t>Mid</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>18</v>
+        <v>286</v>
       </c>
       <c r="K49" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="L49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>1.5.2</t>
+          <t>1.4.1.5</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6761,17 +6940,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1.5.4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Brand Style &amp; Usage Guidelines</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -6779,42 +6958,30 @@
           <t>Brand Style &amp; Usage Guidelines</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>client_review</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Account Manager</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Mid</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
-        <v>48</v>
+        <v>382</v>
       </c>
       <c r="K50" t="n">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="L50" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>1.5.3</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Advanced/T1_LargeVolume</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6824,7 +6991,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1.5.5</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -6834,7 +7001,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -6844,36 +7011,24 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>brand_identity</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Designer</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Mid</t>
-        </is>
-      </c>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
-        <v>83</v>
+        <v>382</v>
       </c>
       <c r="K51" t="n">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>1.5.4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -6887,17 +7042,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1.5.6</t>
+          <t>1.5.1.1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>color</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6907,12 +7062,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>color</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6926,17 +7081,17 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>182</v>
+        <v>20</v>
       </c>
       <c r="K52" t="n">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>1.5.5</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -6950,17 +7105,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1.5.7</t>
+          <t>1.5.1.2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>treatment</t>
+          <t>qa</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -6970,40 +7125,355 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>General</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>treatment</t>
+          <t>qa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Creative Director</t>
+          <t>QA Specialist</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Lead/Director</t>
+          <t>Mid</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="K53" t="n">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>1.5.6</t>
+          <t>1.5.1.1</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Vascano Tequila - RFP Creative Services 2022 (8)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1.5.1.3</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1.5.1</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>internal_review</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Brand Style &amp; Usage Guidelines</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>internal_review</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Art Director</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Lead/Director</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>18</v>
+      </c>
+      <c r="K54" t="n">
+        <v>169</v>
+      </c>
+      <c r="L54" t="n">
+        <v>2</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>1.5.1.2</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Vascano Tequila - RFP Creative Services 2022 (8)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1.5.1.4</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1.5.1</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>client_review</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Brand Style &amp; Usage Guidelines</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>client_review</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Account Manager</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>48</v>
+      </c>
+      <c r="K55" t="n">
+        <v>171</v>
+      </c>
+      <c r="L55" t="n">
+        <v>3</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>1.5.1.3</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Vascano Tequila - RFP Creative Services 2022 (8)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1.5.1.5</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1.5.1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>brand_identity</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Brand Style &amp; Usage Guidelines</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>brand_identity</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Designer</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>83</v>
+      </c>
+      <c r="K56" t="n">
+        <v>174</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>1.5.1.4</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Vascano Tequila - RFP Creative Services 2022 (8)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1.5.1.6</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1.5.1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>style_guide</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Brand Style &amp; Usage Guidelines</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>style_guide</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Designer</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>182</v>
+      </c>
+      <c r="K57" t="n">
+        <v>174</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>1.5.1.5</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Vascano Tequila - RFP Creative Services 2022 (8)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1.5.1.7</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1.5.1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>treatment</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Brand Style &amp; Usage Guidelines</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>treatment</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Creative Director</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Lead/Director</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>23</v>
+      </c>
+      <c r="K58" t="n">
+        <v>174</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>1.5.1.6</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Vascano Tequila - RFP Creative Services 2022 (8) - Scenarios A & B - Workfront Export.xlsx
+++ b/Vascano Tequila - RFP Creative Services 2022 (8) - Scenarios A & B - Workfront Export.xlsx
@@ -657,7 +657,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>Accessibility Audit</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>Accessibility Audit</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Accessibility QA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Accessibility QA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Code Review</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Code Review</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>Analytics Audit</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>Analytics Audit</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>design_prod</t>
+          <t>Design Consult</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>design_prod</t>
+          <t>Design Consult</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Accessibility QA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Accessibility QA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Code Review</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Code Review</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>design_prod</t>
+          <t>Design Consult</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>design_prod</t>
+          <t>Design Consult</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Accessibility QA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Accessibility QA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Code Review</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Code Review</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA Cycle</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA Cycle</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Define &amp; Configure Goals</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Define &amp; Configure Goals</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA Cycle</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA Cycle</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Event Schema &amp; Tagging</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Event Schema &amp; Tagging</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Spec QA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Spec QA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Pixel Setup (GTM)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Pixel Setup (GTM)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA Cycle</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA Cycle</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Migrate UA Goals → GA4 Conversions</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Migrate UA Goals → GA4 Conversions</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA Cycle</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA Cycle</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Implement Tags/Events</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Implement Tags/Events</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Event Config</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Event Config</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Publish &amp; Smoke Test</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Publish &amp; Smoke Test</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Cross-domain Config</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Cross-domain Config</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Ecommerce Data Layer</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Ecommerce Data Layer</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA Cycle</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA Cycle</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>GA4 Property Setup</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>GA4 Property Setup</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>Rights/License Research</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>Rights/License Research</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Usage Notes</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Usage Notes</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Script Polish</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Script Polish</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>VO Session</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>VO Session</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>edit</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>edit</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>edit</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>edit</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>edit</t>
+          <t>VO Edit</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>edit</t>
+          <t>VO Edit</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>sound</t>
+          <t>Mix</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>sound</t>
+          <t>Mix</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>motion</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>motion</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>retouch</t>
+          <t>Retouch</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>retouch</t>
+          <t>Retouch</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>retouch</t>
+          <t>Retouch</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>retouch</t>
+          <t>Retouch</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>sound</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>sound</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>sound</t>
+          <t>Music Search &amp; License</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>sound</t>
+          <t>Music Search &amp; License</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA (Tech &amp; Content)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA (Tech &amp; Content)</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Final Checklist &amp; Upload</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Final Checklist &amp; Upload</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>analytics_tagging</t>
+          <t>Change Orders &amp; Tracking</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>analytics_tagging</t>
+          <t>Change Orders &amp; Tracking</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Invoice Reconciliation</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Invoice Reconciliation</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Cutdowns (2-3)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Cutdowns (2-3)</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review Coordination</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review Coordination</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review Coordination</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review Coordination</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>notes_triage</t>
+          <t>Notes Triage</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>notes_triage</t>
+          <t>Notes Triage</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>library</t>
+          <t>Post Support</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>library</t>
+          <t>Post Support</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>library</t>
+          <t>Post Support</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>library</t>
+          <t>Post Support</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>library</t>
+          <t>Post Support</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>library</t>
+          <t>Post Support</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Post Support</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Post Support</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Post Support</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6969,7 +6969,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Post Support</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>brief</t>
+          <t>Wardrobe Brief</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>brief</t>
+          <t>Wardrobe Brief</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7245,7 +7245,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>deck_build</t>
+          <t>Content Draft</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>deck_build</t>
+          <t>Content Draft</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Deck Build</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Deck Build</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>design_prod</t>
+          <t>Schema Design</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>design_prod</t>
+          <t>Schema Design</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Distribution &amp; Notes</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Distribution &amp; Notes</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8271,7 +8271,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8385,7 +8385,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Schedule Management</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Schedule Management</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8547,7 +8547,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Quality Check (QC)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Quality Check (QC)</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Daily Wrap Notes</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Daily Wrap Notes</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -8838,7 +8838,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Internal Crit</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Internal Crit</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -8952,7 +8952,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>prepro_coord</t>
+          <t>Approvals/Holds</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9081,7 +9081,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>prepro_coord</t>
+          <t>Approvals/Holds</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>prepro_coord</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -9195,7 +9195,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>prepro_coord</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>prepro_coord</t>
+          <t>Approvals &amp; Holds</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>prepro_coord</t>
+          <t>Approvals &amp; Holds</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9408,7 +9408,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>edit</t>
+          <t>Editorial Milestones</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>edit</t>
+          <t>Editorial Milestones</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Delivery Timeline</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Delivery Timeline</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Ideation Sprint</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Ideation Sprint</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -9789,7 +9789,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -9837,7 +9837,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>analytics_tagging</t>
+          <t>Inventory &amp; Tracking</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>analytics_tagging</t>
+          <t>Inventory &amp; Tracking</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10077,7 +10077,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -10092,7 +10092,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Chain of Custody</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -10155,7 +10155,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Chain of Custody</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10254,7 +10254,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>analytics_tagging</t>
+          <t>Filing &amp; Tracking</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10269,7 +10269,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>analytics_tagging</t>
+          <t>Filing &amp; Tracking</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10317,7 +10317,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Deal Memos &amp; Contracts</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10332,7 +10332,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Deal Memos &amp; Contracts</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>community_mgmt</t>
+          <t>Briefing Docs</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>community_mgmt</t>
+          <t>Briefing Docs</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10494,7 +10494,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10572,7 +10572,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -10671,7 +10671,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -10734,7 +10734,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -10749,7 +10749,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Look Dev &amp; References</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Look Dev &amp; References</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -10860,7 +10860,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>Style Guide (lite)</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -10875,7 +10875,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>Style Guide (lite)</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -10974,7 +10974,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11037,7 +11037,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -11052,7 +11052,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Ideation Sprint</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -11115,7 +11115,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Ideation Sprint</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11277,7 +11277,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>SOW/CO Draft &amp; Negotiate</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>SOW/CO Draft &amp; Negotiate</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11454,7 +11454,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -11517,7 +11517,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -11532,7 +11532,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -11580,7 +11580,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Distribution &amp; Confirmation</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -11595,7 +11595,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Distribution &amp; Confirmation</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -11694,7 +11694,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -11709,7 +11709,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>status_meeting</t>
+          <t>Run Meeting &amp; Notes</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -11835,7 +11835,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>status_meeting</t>
+          <t>Run Meeting &amp; Notes</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -11883,7 +11883,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Agenda &amp; Materials</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -11898,7 +11898,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Agenda &amp; Materials</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -11997,7 +11997,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Notes &amp; Shareout</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Notes &amp; Shareout</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Pre-Production Support</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -12126,7 +12126,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Pre-Production Support</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12276,7 +12276,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12390,7 +12390,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>retouch</t>
+          <t>Compositing/Retouch</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -12405,7 +12405,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>retouch</t>
+          <t>Compositing/Retouch</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -12453,7 +12453,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -12516,7 +12516,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -12531,7 +12531,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -12579,7 +12579,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Mockup Scenarios (3-4)</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -12594,7 +12594,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Mockup Scenarios (3-4)</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -12693,7 +12693,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Quality Check (Specs/Accessibility)</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -12708,7 +12708,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Quality Check (Specs/Accessibility)</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -12771,7 +12771,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -12834,7 +12834,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Logo Exploration (6-8 dirs)</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Logo Exploration (6-8 dirs)</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -12996,7 +12996,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Quality Check (Specs/Accessibility)</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Quality Check (Specs/Accessibility)</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13059,7 +13059,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -13074,7 +13074,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -13137,7 +13137,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -13200,7 +13200,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -13299,7 +13299,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -13362,7 +13362,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -13377,7 +13377,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13425,7 +13425,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Messaging Cornerstones Draft</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -13440,7 +13440,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Messaging Cornerstones Draft</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -13539,7 +13539,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -13554,7 +13554,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -13617,7 +13617,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -13665,7 +13665,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Export &amp; Spec</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -13680,7 +13680,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Export &amp; Spec</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -13842,7 +13842,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -13857,7 +13857,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Curate Moodboard</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Curate Moodboard</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14019,7 +14019,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -14034,7 +14034,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -14097,7 +14097,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -14145,7 +14145,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Shortlist &amp; Rationale</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -14160,7 +14160,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Shortlist &amp; Rationale</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -14322,7 +14322,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -14337,7 +14337,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Build Repeating Tiles</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Build Repeating Tiles</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -14499,7 +14499,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -14514,7 +14514,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -14562,7 +14562,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -14577,7 +14577,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -14625,7 +14625,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Compositions (2-3)</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -14640,7 +14640,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Compositions (2-3)</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -14790,7 +14790,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -14805,7 +14805,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -14904,7 +14904,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Quality Check (Specs/Accessibility)</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -14919,7 +14919,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Quality Check (Specs/Accessibility)</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -14967,7 +14967,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -14982,7 +14982,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15030,7 +15030,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -15045,7 +15045,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15093,7 +15093,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -15108,7 +15108,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -15207,7 +15207,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Quality Check (Specs/Accessibility)</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -15222,7 +15222,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Quality Check (Specs/Accessibility)</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -15270,7 +15270,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -15285,7 +15285,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -15333,7 +15333,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -15348,7 +15348,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -15396,7 +15396,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -15411,7 +15411,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -15510,7 +15510,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -15525,7 +15525,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -15573,7 +15573,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -15588,7 +15588,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -15636,7 +15636,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>Outline &amp; Examples</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -15651,7 +15651,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>Outline &amp; Examples</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -15750,7 +15750,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -15765,7 +15765,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -15813,7 +15813,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -15828,7 +15828,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -15876,7 +15876,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>Style Tile Build</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -15891,7 +15891,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>Style Tile Build</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -15990,7 +15990,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -16005,7 +16005,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -16116,7 +16116,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>Examples &amp; Callouts</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -16131,7 +16131,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>Examples &amp; Callouts</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -16230,7 +16230,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -16245,7 +16245,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -16293,7 +16293,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -16308,7 +16308,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -16356,7 +16356,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>Examples &amp; Callouts</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>Examples &amp; Callouts</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -16485,7 +16485,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -16533,7 +16533,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -16548,7 +16548,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -16596,7 +16596,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>Direction Pages</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -16611,7 +16611,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>Direction Pages</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -16725,7 +16725,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -16773,7 +16773,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -16788,7 +16788,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -16836,7 +16836,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -16851,7 +16851,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -16950,7 +16950,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -16965,7 +16965,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -17013,7 +17013,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -17028,7 +17028,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -17076,7 +17076,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -17091,7 +17091,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -17190,7 +17190,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>treatment</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -17205,7 +17205,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>treatment</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -17477,7 +17477,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>Accessibility Audit</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -17492,7 +17492,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>Accessibility Audit</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -17540,7 +17540,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Accessibility QA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -17555,7 +17555,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Accessibility QA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -17603,7 +17603,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Code Review</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -17618,7 +17618,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Code Review</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -17717,7 +17717,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>Analytics Audit</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -17732,7 +17732,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>Analytics Audit</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -17831,7 +17831,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -17846,7 +17846,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -17945,7 +17945,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>design_prod</t>
+          <t>Design Consult</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -17960,7 +17960,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>design_prod</t>
+          <t>Design Consult</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -18008,7 +18008,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Accessibility QA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -18023,7 +18023,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Accessibility QA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -18071,7 +18071,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Code Review</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -18086,7 +18086,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Code Review</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -18185,7 +18185,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>design_prod</t>
+          <t>Design Consult</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -18200,7 +18200,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>design_prod</t>
+          <t>Design Consult</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -18248,7 +18248,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Accessibility QA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -18263,7 +18263,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Accessibility QA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -18311,7 +18311,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Code Review</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -18326,7 +18326,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Code Review</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -18425,7 +18425,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA Cycle</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -18440,7 +18440,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA Cycle</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -18488,7 +18488,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Define &amp; Configure Goals</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -18503,7 +18503,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Define &amp; Configure Goals</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -18602,7 +18602,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA Cycle</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -18617,7 +18617,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA Cycle</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -18665,7 +18665,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Event Schema &amp; Tagging</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Event Schema &amp; Tagging</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -18779,7 +18779,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Spec QA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -18794,7 +18794,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Spec QA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -18842,7 +18842,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Pixel Setup (GTM)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -18857,7 +18857,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Pixel Setup (GTM)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -18956,7 +18956,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA Cycle</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -18971,7 +18971,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA Cycle</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -19019,7 +19019,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Migrate UA Goals → GA4 Conversions</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -19034,7 +19034,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Migrate UA Goals → GA4 Conversions</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -19133,7 +19133,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA Cycle</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -19148,7 +19148,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA Cycle</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -19196,7 +19196,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Implement Tags/Events</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -19211,7 +19211,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Implement Tags/Events</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -19310,7 +19310,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -19325,7 +19325,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -19373,7 +19373,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Event Config</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -19388,7 +19388,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Event Config</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -19487,7 +19487,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Publish &amp; Smoke Test</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -19502,7 +19502,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Publish &amp; Smoke Test</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -19601,7 +19601,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -19664,7 +19664,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Cross-domain Config</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -19679,7 +19679,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Cross-domain Config</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -19778,7 +19778,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -19793,7 +19793,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Ecommerce Data Layer</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -19856,7 +19856,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Ecommerce Data Layer</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -19955,7 +19955,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA Cycle</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA Cycle</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -20018,7 +20018,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>GA4 Property Setup</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -20033,7 +20033,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>GA4 Property Setup</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -20183,7 +20183,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>Rights/License Research</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -20198,7 +20198,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>Rights/License Research</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -20246,7 +20246,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Usage Notes</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -20261,7 +20261,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Usage Notes</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -20360,7 +20360,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Script Polish</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -20375,7 +20375,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Script Polish</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -20423,7 +20423,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>VO Session</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -20438,7 +20438,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>VO Session</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -20537,7 +20537,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>edit</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -20552,7 +20552,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>edit</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -20651,7 +20651,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>edit</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -20666,7 +20666,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>edit</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -20765,7 +20765,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>edit</t>
+          <t>VO Edit</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -20780,7 +20780,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>edit</t>
+          <t>VO Edit</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -20828,7 +20828,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>sound</t>
+          <t>Mix</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -20843,7 +20843,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>sound</t>
+          <t>Mix</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -20891,7 +20891,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -20906,7 +20906,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -20954,7 +20954,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -20969,7 +20969,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -21032,7 +21032,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -21131,7 +21131,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>motion</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -21146,7 +21146,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>motion</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -21245,7 +21245,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -21260,7 +21260,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -21359,7 +21359,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -21374,7 +21374,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -21473,7 +21473,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>retouch</t>
+          <t>Retouch</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -21488,7 +21488,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>retouch</t>
+          <t>Retouch</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -21536,7 +21536,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -21551,7 +21551,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -21599,7 +21599,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -21614,7 +21614,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -21662,7 +21662,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -21677,7 +21677,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -21776,7 +21776,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>retouch</t>
+          <t>Retouch</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -21791,7 +21791,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>retouch</t>
+          <t>Retouch</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -21839,7 +21839,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -21902,7 +21902,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -21917,7 +21917,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -21965,7 +21965,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -21980,7 +21980,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -22079,7 +22079,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>sound</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -22094,7 +22094,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>sound</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -22193,7 +22193,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>sound</t>
+          <t>Music Search &amp; License</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -22208,7 +22208,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>sound</t>
+          <t>Music Search &amp; License</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -22307,7 +22307,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA (Tech &amp; Content)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -22322,7 +22322,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>QA (Tech &amp; Content)</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -22370,7 +22370,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Final Checklist &amp; Upload</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -22385,7 +22385,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Final Checklist &amp; Upload</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>analytics_tagging</t>
+          <t>Change Orders &amp; Tracking</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -22499,7 +22499,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>analytics_tagging</t>
+          <t>Change Orders &amp; Tracking</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -22547,7 +22547,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -22562,7 +22562,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -22610,7 +22610,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -22625,7 +22625,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -22673,7 +22673,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Invoice Reconciliation</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -22688,7 +22688,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Invoice Reconciliation</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -22787,7 +22787,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -22802,7 +22802,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -22850,7 +22850,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -22865,7 +22865,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -22913,7 +22913,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Cutdowns (2-3)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -22928,7 +22928,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Cutdowns (2-3)</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -23027,7 +23027,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review Coordination</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -23042,7 +23042,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review Coordination</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -23141,7 +23141,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review Coordination</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -23156,7 +23156,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review Coordination</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -23204,7 +23204,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>notes_triage</t>
+          <t>Notes Triage</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -23219,7 +23219,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>notes_triage</t>
+          <t>Notes Triage</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -23318,7 +23318,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>library</t>
+          <t>Post Support</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -23333,7 +23333,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>library</t>
+          <t>Post Support</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -23432,7 +23432,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>library</t>
+          <t>Post Support</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -23447,7 +23447,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>library</t>
+          <t>Post Support</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -23546,7 +23546,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>library</t>
+          <t>Post Support</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -23561,7 +23561,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>library</t>
+          <t>Post Support</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -23660,7 +23660,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Post Support</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -23675,7 +23675,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Post Support</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -23774,7 +23774,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Post Support</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Post Support</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -23939,7 +23939,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>brief</t>
+          <t>Wardrobe Brief</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>brief</t>
+          <t>Wardrobe Brief</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -24002,7 +24002,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -24017,7 +24017,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -24065,7 +24065,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -24080,7 +24080,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -24128,7 +24128,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -24143,7 +24143,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -24242,7 +24242,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>deck_build</t>
+          <t>Content Draft</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -24257,7 +24257,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>deck_build</t>
+          <t>Content Draft</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -24305,7 +24305,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Deck Build</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -24320,7 +24320,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Deck Build</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -24368,7 +24368,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -24383,7 +24383,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -24431,7 +24431,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -24446,7 +24446,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -24545,7 +24545,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>design_prod</t>
+          <t>Schema Design</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -24560,7 +24560,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>design_prod</t>
+          <t>Schema Design</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -24608,7 +24608,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -24623,7 +24623,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -24671,7 +24671,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -24686,7 +24686,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -24734,7 +24734,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Distribution &amp; Notes</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -24749,7 +24749,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Distribution &amp; Notes</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -24848,7 +24848,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -24863,7 +24863,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -24962,7 +24962,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -24977,7 +24977,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -25076,7 +25076,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -25091,7 +25091,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -25190,7 +25190,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -25205,7 +25205,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -25304,7 +25304,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Schedule Management</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -25319,7 +25319,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Schedule Management</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -25367,7 +25367,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Quality Check (QC)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -25382,7 +25382,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Quality Check (QC)</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -25430,7 +25430,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Daily Wrap Notes</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -25445,7 +25445,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Daily Wrap Notes</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -25544,7 +25544,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -25559,7 +25559,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -25658,7 +25658,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Internal Crit</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -25673,7 +25673,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Internal Crit</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -25787,7 +25787,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>prepro_docs</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -25886,7 +25886,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>prepro_coord</t>
+          <t>Approvals/Holds</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -25901,7 +25901,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>prepro_coord</t>
+          <t>Approvals/Holds</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -26000,7 +26000,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>prepro_coord</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -26015,7 +26015,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>prepro_coord</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -26114,7 +26114,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>prepro_coord</t>
+          <t>Approvals &amp; Holds</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -26129,7 +26129,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>prepro_coord</t>
+          <t>Approvals &amp; Holds</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -26228,7 +26228,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>edit</t>
+          <t>Editorial Milestones</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -26243,7 +26243,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>edit</t>
+          <t>Editorial Milestones</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -26291,7 +26291,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -26306,7 +26306,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -26354,7 +26354,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -26369,7 +26369,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -26417,7 +26417,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Delivery Timeline</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -26432,7 +26432,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Delivery Timeline</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -26531,7 +26531,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Ideation Sprint</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -26546,7 +26546,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>development</t>
+          <t>Ideation Sprint</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -26594,7 +26594,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -26609,7 +26609,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -26657,7 +26657,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -26672,7 +26672,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -26771,7 +26771,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>analytics_tagging</t>
+          <t>Inventory &amp; Tracking</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -26786,7 +26786,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>analytics_tagging</t>
+          <t>Inventory &amp; Tracking</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -26834,7 +26834,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -26849,7 +26849,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -26897,7 +26897,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -26912,7 +26912,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -26960,7 +26960,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Chain of Custody</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -26975,7 +26975,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Chain of Custody</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -27074,7 +27074,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>analytics_tagging</t>
+          <t>Filing &amp; Tracking</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -27089,7 +27089,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>analytics_tagging</t>
+          <t>Filing &amp; Tracking</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -27137,7 +27137,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Deal Memos &amp; Contracts</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -27152,7 +27152,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Deal Memos &amp; Contracts</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -27251,7 +27251,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>community_mgmt</t>
+          <t>Briefing Docs</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -27266,7 +27266,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>community_mgmt</t>
+          <t>Briefing Docs</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -27329,7 +27329,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -27392,7 +27392,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -27491,7 +27491,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -27506,7 +27506,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -27554,7 +27554,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -27569,7 +27569,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -27617,7 +27617,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Look Dev &amp; References</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -27632,7 +27632,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Look Dev &amp; References</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -27680,7 +27680,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>Style Guide (lite)</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -27695,7 +27695,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>Style Guide (lite)</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -27794,7 +27794,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -27857,7 +27857,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -27872,7 +27872,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -27920,7 +27920,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Ideation Sprint</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -27935,7 +27935,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Ideation Sprint</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -28034,7 +28034,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -28049,7 +28049,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -28097,7 +28097,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -28112,7 +28112,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -28160,7 +28160,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>SOW/CO Draft &amp; Negotiate</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -28175,7 +28175,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>SOW/CO Draft &amp; Negotiate</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -28274,7 +28274,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -28289,7 +28289,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -28337,7 +28337,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -28352,7 +28352,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -28400,7 +28400,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Distribution &amp; Confirmation</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -28415,7 +28415,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Distribution &amp; Confirmation</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -28514,7 +28514,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -28529,7 +28529,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -28577,7 +28577,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -28592,7 +28592,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -28640,7 +28640,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>status_meeting</t>
+          <t>Run Meeting &amp; Notes</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -28655,7 +28655,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>status_meeting</t>
+          <t>Run Meeting &amp; Notes</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -28703,7 +28703,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Agenda &amp; Materials</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -28718,7 +28718,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Agenda &amp; Materials</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -28817,7 +28817,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Notes &amp; Shareout</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -28832,7 +28832,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Notes &amp; Shareout</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -28931,7 +28931,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Pre-Production Support</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -28946,7 +28946,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Pre-Production Support</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -29096,7 +29096,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -29111,7 +29111,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -29210,7 +29210,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>retouch</t>
+          <t>Compositing/Retouch</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -29225,7 +29225,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>retouch</t>
+          <t>Compositing/Retouch</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -29273,7 +29273,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -29288,7 +29288,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -29336,7 +29336,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -29351,7 +29351,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -29399,7 +29399,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Mockup Scenarios (3-4)</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Mockup Scenarios (3-4)</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -29513,7 +29513,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Quality Check (Specs/Accessibility)</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -29528,7 +29528,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Quality Check (Specs/Accessibility)</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -29576,7 +29576,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -29591,7 +29591,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -29639,7 +29639,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -29654,7 +29654,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -29702,7 +29702,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Logo Exploration (6-8 dirs)</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -29717,7 +29717,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Logo Exploration (6-8 dirs)</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -29816,7 +29816,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Quality Check (Specs/Accessibility)</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -29831,7 +29831,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Quality Check (Specs/Accessibility)</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -29879,7 +29879,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -29894,7 +29894,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -29942,7 +29942,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -29957,7 +29957,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -30005,7 +30005,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -30020,7 +30020,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -30119,7 +30119,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -30134,7 +30134,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -30182,7 +30182,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -30197,7 +30197,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -30245,7 +30245,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Messaging Cornerstones Draft</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -30260,7 +30260,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Messaging Cornerstones Draft</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -30359,7 +30359,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -30374,7 +30374,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -30422,7 +30422,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -30437,7 +30437,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -30485,7 +30485,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Export &amp; Spec</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Export &amp; Spec</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -30599,7 +30599,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -30614,7 +30614,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -30662,7 +30662,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -30677,7 +30677,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -30725,7 +30725,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Curate Moodboard</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -30740,7 +30740,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Curate Moodboard</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -30839,7 +30839,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -30854,7 +30854,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -30902,7 +30902,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -30917,7 +30917,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -30965,7 +30965,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Shortlist &amp; Rationale</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -30980,7 +30980,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Shortlist &amp; Rationale</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -31079,7 +31079,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -31142,7 +31142,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -31157,7 +31157,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -31205,7 +31205,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Build Repeating Tiles</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -31220,7 +31220,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Build Repeating Tiles</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -31319,7 +31319,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -31334,7 +31334,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -31382,7 +31382,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -31397,7 +31397,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -31445,7 +31445,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Compositions (2-3)</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -31460,7 +31460,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Compositions (2-3)</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -31610,7 +31610,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -31625,7 +31625,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Quality Check (Specs/Accessibility)</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -31739,7 +31739,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Quality Check (Specs/Accessibility)</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -31787,7 +31787,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -31802,7 +31802,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -31850,7 +31850,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -31865,7 +31865,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -31913,7 +31913,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -31928,7 +31928,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -32027,7 +32027,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Quality Check (Specs/Accessibility)</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -32042,7 +32042,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>qa</t>
+          <t>Quality Check (Specs/Accessibility)</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -32090,7 +32090,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -32105,7 +32105,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -32153,7 +32153,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -32168,7 +32168,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -32216,7 +32216,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -32231,7 +32231,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -32330,7 +32330,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -32345,7 +32345,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -32393,7 +32393,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -32408,7 +32408,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -32456,7 +32456,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>Outline &amp; Examples</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -32471,7 +32471,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>Outline &amp; Examples</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -32570,7 +32570,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -32585,7 +32585,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -32633,7 +32633,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -32648,7 +32648,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -32696,7 +32696,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>Style Tile Build</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -32711,7 +32711,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>Style Tile Build</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -32810,7 +32810,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -32825,7 +32825,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -32873,7 +32873,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -32888,7 +32888,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -32936,7 +32936,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>Examples &amp; Callouts</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -32951,7 +32951,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>Examples &amp; Callouts</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -33050,7 +33050,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -33065,7 +33065,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -33113,7 +33113,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -33128,7 +33128,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -33176,7 +33176,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>Examples &amp; Callouts</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -33191,7 +33191,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>Examples &amp; Callouts</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -33290,7 +33290,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -33305,7 +33305,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -33353,7 +33353,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -33368,7 +33368,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -33416,7 +33416,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>Direction Pages</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -33431,7 +33431,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>Direction Pages</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -33530,7 +33530,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -33545,7 +33545,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -33593,7 +33593,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -33608,7 +33608,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -33656,7 +33656,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -33671,7 +33671,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>brand_identity</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -33770,7 +33770,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -33785,7 +33785,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>internal_review</t>
+          <t>Internal Review &amp; Critique</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -33833,7 +33833,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -33848,7 +33848,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>client_review</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -33896,7 +33896,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -33911,7 +33911,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>style_guide</t>
+          <t>Final Packaging</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -34010,7 +34010,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>treatment</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -34025,7 +34025,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>treatment</t>
+          <t>Client Review &amp; Revisions</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">

--- a/Vascano Tequila - RFP Creative Services 2022 (8) - Scenarios A & B - Workfront Export.xlsx
+++ b/Vascano Tequila - RFP Creative Services 2022 (8) - Scenarios A & B - Workfront Export.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O284"/>
+  <dimension ref="A1:Q284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,6 +503,16 @@
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Rate_USD</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Price_USD</t>
         </is>
       </c>
     </row>
@@ -540,6 +550,8 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -587,6 +599,12 @@
           <t>Core/T2_MediumVolume</t>
         </is>
       </c>
+      <c r="P3" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>42048.65</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -638,6 +656,12 @@
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>9277.75</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -701,6 +725,12 @@
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>314.5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -764,6 +794,12 @@
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>786.25</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -827,6 +863,12 @@
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>8177</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -878,6 +920,12 @@
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3145</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -941,6 +989,12 @@
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3145</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -992,6 +1046,12 @@
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3145</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1055,6 +1115,12 @@
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3145</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1106,6 +1172,12 @@
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>7940.2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1169,6 +1241,12 @@
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>629</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1232,6 +1310,12 @@
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1021.2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1295,6 +1379,12 @@
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>6290</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1346,6 +1436,12 @@
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>7940.2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1409,6 +1505,12 @@
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
+      <c r="P17" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>629</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1472,6 +1574,12 @@
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
+      <c r="P18" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1021.2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1535,6 +1643,12 @@
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>6290</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1586,6 +1700,12 @@
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1256.15</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1649,6 +1769,12 @@
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
+      <c r="P21" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>471.75</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1712,6 +1838,12 @@
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>784.4</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1763,6 +1895,12 @@
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1256.15</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1826,6 +1964,12 @@
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>471.75</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1889,6 +2033,12 @@
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
+      <c r="P25" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>784.4</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1940,6 +2090,12 @@
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
+      <c r="P26" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>863.95</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2003,6 +2159,12 @@
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
+      <c r="P27" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>471.75</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2066,6 +2228,12 @@
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>392.2</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2117,6 +2285,12 @@
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1256.15</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2180,6 +2354,12 @@
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>471.75</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2243,6 +2423,12 @@
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>784.4</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2294,6 +2480,12 @@
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
+      <c r="P32" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1256.15</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2357,6 +2549,12 @@
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
+      <c r="P33" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>471.75</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2420,6 +2618,12 @@
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
+      <c r="P34" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>784.4</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2471,6 +2675,12 @@
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
+      <c r="P35" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>863.95</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2534,6 +2744,12 @@
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
+      <c r="P36" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>471.75</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2597,6 +2813,12 @@
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
+      <c r="P37" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>392.2</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2648,6 +2870,12 @@
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
+      <c r="P38" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>863.95</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2711,6 +2939,12 @@
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
+      <c r="P39" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>863.95</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2762,6 +2996,12 @@
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
+      <c r="P40" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>863.95</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2825,6 +3065,12 @@
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
+      <c r="P41" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>471.75</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2888,6 +3134,12 @@
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
+      <c r="P42" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>392.2</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2939,6 +3191,12 @@
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
+      <c r="P43" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>863.95</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3002,6 +3260,12 @@
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
+      <c r="P44" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>471.75</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3065,6 +3329,12 @@
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
+      <c r="P45" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>392.2</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3116,6 +3386,12 @@
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
+      <c r="P46" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1256.15</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3179,6 +3455,12 @@
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
+      <c r="P47" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>471.75</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3242,6 +3524,12 @@
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
+      <c r="P48" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>784.4</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3293,6 +3581,12 @@
           <t>Core/T2_MediumVolume</t>
         </is>
       </c>
+      <c r="P49" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>34841.05</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3344,6 +3638,12 @@
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
+      <c r="P50" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>392.2</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3407,6 +3707,12 @@
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
+      <c r="P51" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>157.25</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3470,6 +3776,12 @@
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
+      <c r="P52" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>234.95</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3521,6 +3833,12 @@
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
+      <c r="P53" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>862.1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3584,6 +3902,12 @@
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
+      <c r="P54" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>234.95</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3647,6 +3971,12 @@
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
+      <c r="P55" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>627.15</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3698,6 +4028,12 @@
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
+      <c r="P56" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>3145</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3761,6 +4097,12 @@
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
+      <c r="P57" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>3145</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3812,6 +4154,12 @@
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
+      <c r="P58" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>4717.5</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3875,6 +4223,12 @@
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
+      <c r="P59" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>4717.5</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3926,6 +4280,12 @@
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
+      <c r="P60" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>3102.45</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3989,6 +4349,12 @@
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
+      <c r="P61" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>1572.5</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4052,6 +4418,12 @@
       </c>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
+      <c r="P62" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>392.2</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4115,6 +4487,12 @@
       </c>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
+      <c r="P63" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>275.65</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4178,6 +4556,12 @@
       </c>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
+      <c r="P64" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>469.9</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4241,6 +4625,12 @@
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
+      <c r="P65" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>392.2</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4292,6 +4682,12 @@
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
+      <c r="P66" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>3145</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4355,6 +4751,12 @@
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
+      <c r="P67" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>3145</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4406,6 +4808,12 @@
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
+      <c r="P68" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>2121.95</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4469,6 +4877,12 @@
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
+      <c r="P69" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>2121.95</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4520,6 +4934,12 @@
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
+      <c r="P70" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>2121.95</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4583,6 +5003,12 @@
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
+      <c r="P71" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>2121.95</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4634,6 +5060,12 @@
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
+      <c r="P72" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>1924</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4697,6 +5129,12 @@
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
+      <c r="P73" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>786.25</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4760,6 +5198,12 @@
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
+      <c r="P74" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>275.65</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4823,6 +5267,12 @@
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
+      <c r="P75" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>469.9</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4886,6 +5336,12 @@
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
+      <c r="P76" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>392.2</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4937,6 +5393,12 @@
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
+      <c r="P77" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>1924</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5000,6 +5462,12 @@
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
+      <c r="P78" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>786.25</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5063,6 +5531,12 @@
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
+      <c r="P79" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>275.65</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5126,6 +5600,12 @@
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
+      <c r="P80" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>469.9</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5189,6 +5669,12 @@
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
+      <c r="P81" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>392.2</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5240,6 +5726,12 @@
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
+      <c r="P82" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>1570.65</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5303,6 +5795,12 @@
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
+      <c r="P83" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>1570.65</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5354,6 +5852,12 @@
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
+      <c r="P84" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>549.45</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5417,6 +5921,12 @@
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
+      <c r="P85" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>549.45</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5468,6 +5978,12 @@
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
+      <c r="P86" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>1256.15</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5531,6 +6047,12 @@
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
+      <c r="P87" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>471.75</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5594,6 +6116,12 @@
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
+      <c r="P88" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>784.4</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5645,6 +6173,12 @@
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
+      <c r="P89" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>1764.9</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5708,6 +6242,12 @@
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
+      <c r="P90" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>157.25</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5771,6 +6311,12 @@
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
+      <c r="P91" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>275.65</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5834,6 +6380,12 @@
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
+      <c r="P92" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>469.9</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5897,6 +6449,12 @@
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
+      <c r="P93" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>862.1</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5948,6 +6506,12 @@
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
+      <c r="P94" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>2081.25</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6011,6 +6575,12 @@
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
+      <c r="P95" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>275.65</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6074,6 +6644,12 @@
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
+      <c r="P96" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>469.9</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6137,6 +6713,12 @@
       </c>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
+      <c r="P97" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>1335.7</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6188,6 +6770,12 @@
       </c>
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
+      <c r="P98" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>704.85</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6251,6 +6839,12 @@
       </c>
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr"/>
+      <c r="P99" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>704.85</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6302,6 +6896,12 @@
       </c>
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr"/>
+      <c r="P100" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>627.15</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6365,6 +6965,12 @@
       </c>
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr"/>
+      <c r="P101" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>469.9</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6428,6 +7034,12 @@
       </c>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr"/>
+      <c r="P102" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>157.25</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6479,6 +7091,12 @@
       </c>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr"/>
+      <c r="P103" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>314.5</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6542,6 +7160,12 @@
       </c>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
+      <c r="P104" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>314.5</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6593,6 +7217,12 @@
       </c>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
+      <c r="P105" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>314.5</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6656,6 +7286,12 @@
       </c>
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr"/>
+      <c r="P106" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>314.5</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6707,6 +7343,12 @@
       </c>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
+      <c r="P107" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>314.5</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6770,6 +7412,12 @@
       </c>
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr"/>
+      <c r="P108" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>314.5</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6821,6 +7469,12 @@
       </c>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
+      <c r="P109" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>943.5</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6884,6 +7538,12 @@
       </c>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr"/>
+      <c r="P110" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>943.5</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6935,6 +7595,12 @@
       </c>
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr"/>
+      <c r="P111" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>943.5</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6998,6 +7664,12 @@
       </c>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
+      <c r="P112" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>943.5</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7049,6 +7721,12 @@
           <t>Core/T2_MediumVolume</t>
         </is>
       </c>
+      <c r="P113" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>73195.25</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7100,6 +7778,12 @@
       </c>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr"/>
+      <c r="P114" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>2234.8</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7163,6 +7847,12 @@
       </c>
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr"/>
+      <c r="P115" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>469.9</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7226,6 +7916,12 @@
       </c>
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr"/>
+      <c r="P116" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>275.65</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7289,6 +7985,12 @@
       </c>
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr"/>
+      <c r="P117" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>469.9</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7352,6 +8054,12 @@
       </c>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
+      <c r="P118" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>1019.35</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7403,6 +8111,12 @@
       </c>
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr"/>
+      <c r="P119" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>4754.5</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7466,6 +8180,12 @@
       </c>
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
+      <c r="P120" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>3774</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7529,6 +8249,12 @@
       </c>
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr"/>
+      <c r="P121" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>234.95</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7592,6 +8318,12 @@
       </c>
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
+      <c r="P122" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>275.65</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7655,6 +8387,12 @@
       </c>
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr"/>
+      <c r="P123" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>469.9</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7706,6 +8444,12 @@
       </c>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
+      <c r="P124" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>2158.95</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7769,6 +8513,12 @@
       </c>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr"/>
+      <c r="P125" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>471.75</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7832,6 +8582,12 @@
       </c>
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr"/>
+      <c r="P126" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>275.65</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7895,6 +8651,12 @@
       </c>
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr"/>
+      <c r="P127" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>469.9</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7958,6 +8720,12 @@
       </c>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr"/>
+      <c r="P128" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>941.65</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -8009,6 +8777,12 @@
       </c>
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr"/>
+      <c r="P129" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>3063.6</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -8072,6 +8846,12 @@
       </c>
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr"/>
+      <c r="P130" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>3063.6</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8123,6 +8903,12 @@
       </c>
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr"/>
+      <c r="P131" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>3063.6</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -8186,6 +8972,12 @@
       </c>
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr"/>
+      <c r="P132" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>3063.6</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8237,6 +9029,12 @@
       </c>
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr"/>
+      <c r="P133" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>4243.9</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -8300,6 +9098,12 @@
       </c>
       <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr"/>
+      <c r="P134" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>4243.9</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -8351,6 +9155,12 @@
       </c>
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr"/>
+      <c r="P135" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>5649.9</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -8414,6 +9224,12 @@
       </c>
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr"/>
+      <c r="P136" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>5649.9</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8465,6 +9281,12 @@
       </c>
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
+      <c r="P137" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>2197.8</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8528,6 +9350,12 @@
       </c>
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr"/>
+      <c r="P138" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>471.75</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8591,6 +9419,12 @@
       </c>
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr"/>
+      <c r="P139" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>471.75</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8654,6 +9488,12 @@
       </c>
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
+      <c r="P140" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>1254.3</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8705,6 +9545,12 @@
       </c>
       <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr"/>
+      <c r="P141" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>3770.3</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -8768,6 +9614,12 @@
       </c>
       <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr"/>
+      <c r="P142" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>3770.3</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8819,6 +9671,12 @@
       </c>
       <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr"/>
+      <c r="P143" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>704.85</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -8882,6 +9740,12 @@
       </c>
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr"/>
+      <c r="P144" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>704.85</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8933,6 +9797,12 @@
       </c>
       <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr"/>
+      <c r="P145" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>2824.95</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -8996,6 +9866,12 @@
       </c>
       <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr"/>
+      <c r="P146" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>2824.95</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -9047,6 +9923,12 @@
       </c>
       <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr"/>
+      <c r="P147" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>2362.45</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -9110,6 +9992,12 @@
       </c>
       <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr"/>
+      <c r="P148" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>2362.45</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -9161,6 +10049,12 @@
       </c>
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr"/>
+      <c r="P149" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>4643.5</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -9224,6 +10118,12 @@
       </c>
       <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr"/>
+      <c r="P150" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>4643.5</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -9275,6 +10175,12 @@
       </c>
       <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr"/>
+      <c r="P151" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>4565.8</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -9338,6 +10244,12 @@
       </c>
       <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr"/>
+      <c r="P152" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>4565.8</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -9389,6 +10301,12 @@
       </c>
       <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr"/>
+      <c r="P153" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>3964.55</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -9452,6 +10370,12 @@
       </c>
       <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr"/>
+      <c r="P154" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>1887</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -9515,6 +10439,12 @@
       </c>
       <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr"/>
+      <c r="P155" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>275.65</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -9578,6 +10508,12 @@
       </c>
       <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr"/>
+      <c r="P156" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>704.85</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -9641,6 +10577,12 @@
       </c>
       <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr"/>
+      <c r="P157" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>1097.05</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -9692,6 +10634,12 @@
       </c>
       <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr"/>
+      <c r="P158" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>3102.45</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -9755,6 +10703,12 @@
       </c>
       <c r="N159" t="inlineStr"/>
       <c r="O159" t="inlineStr"/>
+      <c r="P159" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>2199.65</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -9818,6 +10772,12 @@
       </c>
       <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr"/>
+      <c r="P160" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>275.65</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -9881,6 +10841,12 @@
       </c>
       <c r="N161" t="inlineStr"/>
       <c r="O161" t="inlineStr"/>
+      <c r="P161" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>627.15</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -9932,6 +10898,12 @@
       </c>
       <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr"/>
+      <c r="P162" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>1764.9</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -9995,6 +10967,12 @@
       </c>
       <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr"/>
+      <c r="P163" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>157.25</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -10058,6 +11036,12 @@
       </c>
       <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr"/>
+      <c r="P164" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>275.65</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -10121,6 +11105,12 @@
       </c>
       <c r="N165" t="inlineStr"/>
       <c r="O165" t="inlineStr"/>
+      <c r="P165" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>469.9</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -10184,6 +11174,12 @@
       </c>
       <c r="N166" t="inlineStr"/>
       <c r="O166" t="inlineStr"/>
+      <c r="P166" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>862.1</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -10235,6 +11231,12 @@
       </c>
       <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr"/>
+      <c r="P167" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>627.15</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -10298,6 +11300,12 @@
       </c>
       <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr"/>
+      <c r="P168" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>157.25</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -10361,6 +11369,12 @@
       </c>
       <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr"/>
+      <c r="P169" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>469.9</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -10412,6 +11426,12 @@
       </c>
       <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr"/>
+      <c r="P170" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>2469.75</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -10475,6 +11495,12 @@
       </c>
       <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr"/>
+      <c r="P171" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>1724.2</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -10538,6 +11564,12 @@
       </c>
       <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr"/>
+      <c r="P172" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>275.65</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -10601,6 +11633,12 @@
       </c>
       <c r="N173" t="inlineStr"/>
       <c r="O173" t="inlineStr"/>
+      <c r="P173" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>469.9</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -10652,6 +11690,12 @@
       </c>
       <c r="N174" t="inlineStr"/>
       <c r="O174" t="inlineStr"/>
+      <c r="P174" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>3572.35</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -10715,6 +11759,12 @@
       </c>
       <c r="N175" t="inlineStr"/>
       <c r="O175" t="inlineStr"/>
+      <c r="P175" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>275.65</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -10778,6 +11828,12 @@
       </c>
       <c r="N176" t="inlineStr"/>
       <c r="O176" t="inlineStr"/>
+      <c r="P176" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>469.9</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -10841,6 +11897,12 @@
       </c>
       <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr"/>
+      <c r="P177" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>1019.35</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -10904,6 +11966,12 @@
       </c>
       <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr"/>
+      <c r="P178" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>1807.45</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -10955,6 +12023,12 @@
       </c>
       <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr"/>
+      <c r="P179" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>3888.7</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -11018,6 +12092,12 @@
       </c>
       <c r="N180" t="inlineStr"/>
       <c r="O180" t="inlineStr"/>
+      <c r="P180" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>275.65</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -11081,6 +12161,12 @@
       </c>
       <c r="N181" t="inlineStr"/>
       <c r="O181" t="inlineStr"/>
+      <c r="P181" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>627.15</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -11144,6 +12230,12 @@
       </c>
       <c r="N182" t="inlineStr"/>
       <c r="O182" t="inlineStr"/>
+      <c r="P182" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>2985.9</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -11195,6 +12287,12 @@
       </c>
       <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr"/>
+      <c r="P183" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>2312.5</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -11258,6 +12356,12 @@
       </c>
       <c r="N184" t="inlineStr"/>
       <c r="O184" t="inlineStr"/>
+      <c r="P184" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>275.65</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -11321,6 +12425,12 @@
       </c>
       <c r="N185" t="inlineStr"/>
       <c r="O185" t="inlineStr"/>
+      <c r="P185" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>704.85</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -11384,6 +12494,12 @@
       </c>
       <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr"/>
+      <c r="P186" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>1332</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -11435,6 +12551,12 @@
       </c>
       <c r="N187" t="inlineStr"/>
       <c r="O187" t="inlineStr"/>
+      <c r="P187" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>1842.6</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -11498,6 +12620,12 @@
       </c>
       <c r="N188" t="inlineStr"/>
       <c r="O188" t="inlineStr"/>
+      <c r="P188" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>275.65</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -11561,6 +12689,12 @@
       </c>
       <c r="N189" t="inlineStr"/>
       <c r="O189" t="inlineStr"/>
+      <c r="P189" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>469.9</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -11624,6 +12758,12 @@
       </c>
       <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr"/>
+      <c r="P190" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>1097.05</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -11675,6 +12815,12 @@
       </c>
       <c r="N191" t="inlineStr"/>
       <c r="O191" t="inlineStr"/>
+      <c r="P191" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>2471.6</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -11738,6 +12884,12 @@
       </c>
       <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr"/>
+      <c r="P192" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>275.65</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -11801,6 +12953,12 @@
       </c>
       <c r="N193" t="inlineStr"/>
       <c r="O193" t="inlineStr"/>
+      <c r="P193" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>469.9</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -11864,6 +13022,12 @@
       </c>
       <c r="N194" t="inlineStr"/>
       <c r="O194" t="inlineStr"/>
+      <c r="P194" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>471.75</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -11927,6 +13091,12 @@
       </c>
       <c r="N195" t="inlineStr"/>
       <c r="O195" t="inlineStr"/>
+      <c r="P195" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q195" t="n">
+        <v>1254.3</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -11978,6 +13148,12 @@
       </c>
       <c r="N196" t="inlineStr"/>
       <c r="O196" t="inlineStr"/>
+      <c r="P196" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>704.85</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -12041,6 +13217,12 @@
       </c>
       <c r="N197" t="inlineStr"/>
       <c r="O197" t="inlineStr"/>
+      <c r="P197" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q197" t="n">
+        <v>704.85</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -12092,6 +13274,12 @@
       </c>
       <c r="N198" t="inlineStr"/>
       <c r="O198" t="inlineStr"/>
+      <c r="P198" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q198" t="n">
+        <v>234.95</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -12155,6 +13343,12 @@
       </c>
       <c r="N199" t="inlineStr"/>
       <c r="O199" t="inlineStr"/>
+      <c r="P199" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>234.95</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -12206,6 +13400,12 @@
           <t>Core/T2_MediumVolume</t>
         </is>
       </c>
+      <c r="P200" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>47241.6</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -12257,6 +13457,12 @@
       </c>
       <c r="N201" t="inlineStr"/>
       <c r="O201" t="inlineStr"/>
+      <c r="P201" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>2826.8</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -12320,6 +13526,12 @@
       </c>
       <c r="N202" t="inlineStr"/>
       <c r="O202" t="inlineStr"/>
+      <c r="P202" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>2826.8</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -12371,6 +13583,12 @@
       </c>
       <c r="N203" t="inlineStr"/>
       <c r="O203" t="inlineStr"/>
+      <c r="P203" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>4637.95</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -12434,6 +13652,12 @@
       </c>
       <c r="N204" t="inlineStr"/>
       <c r="O204" t="inlineStr"/>
+      <c r="P204" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>786.25</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -12497,6 +13721,12 @@
       </c>
       <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr"/>
+      <c r="P205" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q205" t="n">
+        <v>236.8</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -12560,6 +13790,12 @@
       </c>
       <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr"/>
+      <c r="P206" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>627.15</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -12623,6 +13859,12 @@
       </c>
       <c r="N207" t="inlineStr"/>
       <c r="O207" t="inlineStr"/>
+      <c r="P207" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>2987.75</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -12674,6 +13916,12 @@
       </c>
       <c r="N208" t="inlineStr"/>
       <c r="O208" t="inlineStr"/>
+      <c r="P208" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>6839.45</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -12737,6 +13985,12 @@
       </c>
       <c r="N209" t="inlineStr"/>
       <c r="O209" t="inlineStr"/>
+      <c r="P209" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>471.75</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -12800,6 +14054,12 @@
       </c>
       <c r="N210" t="inlineStr"/>
       <c r="O210" t="inlineStr"/>
+      <c r="P210" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>236.8</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -12863,6 +14123,12 @@
       </c>
       <c r="N211" t="inlineStr"/>
       <c r="O211" t="inlineStr"/>
+      <c r="P211" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>627.15</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -12926,6 +14192,12 @@
       </c>
       <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr"/>
+      <c r="P212" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>5503.75</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -12977,6 +14249,12 @@
       </c>
       <c r="N213" t="inlineStr"/>
       <c r="O213" t="inlineStr"/>
+      <c r="P213" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>6367.7</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -13040,6 +14318,12 @@
       </c>
       <c r="N214" t="inlineStr"/>
       <c r="O214" t="inlineStr"/>
+      <c r="P214" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>471.75</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -13103,6 +14387,12 @@
       </c>
       <c r="N215" t="inlineStr"/>
       <c r="O215" t="inlineStr"/>
+      <c r="P215" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>236.8</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -13166,6 +14456,12 @@
       </c>
       <c r="N216" t="inlineStr"/>
       <c r="O216" t="inlineStr"/>
+      <c r="P216" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>627.15</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -13229,6 +14525,12 @@
       </c>
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr"/>
+      <c r="P217" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>5032</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -13280,6 +14582,12 @@
       </c>
       <c r="N218" t="inlineStr"/>
       <c r="O218" t="inlineStr"/>
+      <c r="P218" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q218" t="n">
+        <v>4323.45</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -13343,6 +14651,12 @@
       </c>
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr"/>
+      <c r="P219" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>236.8</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -13406,6 +14720,12 @@
       </c>
       <c r="N220" t="inlineStr"/>
       <c r="O220" t="inlineStr"/>
+      <c r="P220" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>784.4</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -13469,6 +14789,12 @@
       </c>
       <c r="N221" t="inlineStr"/>
       <c r="O221" t="inlineStr"/>
+      <c r="P221" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>3302.25</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -13520,6 +14846,12 @@
       </c>
       <c r="N222" t="inlineStr"/>
       <c r="O222" t="inlineStr"/>
+      <c r="P222" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>4952.45</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -13583,6 +14915,12 @@
       </c>
       <c r="N223" t="inlineStr"/>
       <c r="O223" t="inlineStr"/>
+      <c r="P223" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>236.8</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -13646,6 +14984,12 @@
       </c>
       <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr"/>
+      <c r="P224" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>627.15</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -13709,6 +15053,12 @@
       </c>
       <c r="N225" t="inlineStr"/>
       <c r="O225" t="inlineStr"/>
+      <c r="P225" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>4088.5</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -13760,6 +15110,12 @@
       </c>
       <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr"/>
+      <c r="P226" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>4166.2</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -13823,6 +15179,12 @@
       </c>
       <c r="N227" t="inlineStr"/>
       <c r="O227" t="inlineStr"/>
+      <c r="P227" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>236.8</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -13886,6 +15248,12 @@
       </c>
       <c r="N228" t="inlineStr"/>
       <c r="O228" t="inlineStr"/>
+      <c r="P228" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q228" t="n">
+        <v>627.15</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -13949,6 +15317,12 @@
       </c>
       <c r="N229" t="inlineStr"/>
       <c r="O229" t="inlineStr"/>
+      <c r="P229" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q229" t="n">
+        <v>3302.25</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -14000,6 +15374,12 @@
       </c>
       <c r="N230" t="inlineStr"/>
       <c r="O230" t="inlineStr"/>
+      <c r="P230" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q230" t="n">
+        <v>3379.95</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -14063,6 +15443,12 @@
       </c>
       <c r="N231" t="inlineStr"/>
       <c r="O231" t="inlineStr"/>
+      <c r="P231" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q231" t="n">
+        <v>236.8</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -14126,6 +15512,12 @@
       </c>
       <c r="N232" t="inlineStr"/>
       <c r="O232" t="inlineStr"/>
+      <c r="P232" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q232" t="n">
+        <v>784.4</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -14189,6 +15581,12 @@
       </c>
       <c r="N233" t="inlineStr"/>
       <c r="O233" t="inlineStr"/>
+      <c r="P233" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>2358.75</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -14240,6 +15638,12 @@
       </c>
       <c r="N234" t="inlineStr"/>
       <c r="O234" t="inlineStr"/>
+      <c r="P234" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q234" t="n">
+        <v>4637.95</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -14303,6 +15707,12 @@
       </c>
       <c r="N235" t="inlineStr"/>
       <c r="O235" t="inlineStr"/>
+      <c r="P235" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q235" t="n">
+        <v>236.8</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -14366,6 +15776,12 @@
       </c>
       <c r="N236" t="inlineStr"/>
       <c r="O236" t="inlineStr"/>
+      <c r="P236" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q236" t="n">
+        <v>627.15</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -14429,6 +15845,12 @@
       </c>
       <c r="N237" t="inlineStr"/>
       <c r="O237" t="inlineStr"/>
+      <c r="P237" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q237" t="n">
+        <v>3774</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -14480,6 +15902,12 @@
       </c>
       <c r="N238" t="inlineStr"/>
       <c r="O238" t="inlineStr"/>
+      <c r="P238" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q238" t="n">
+        <v>5109.7</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -14543,6 +15971,12 @@
       </c>
       <c r="N239" t="inlineStr"/>
       <c r="O239" t="inlineStr"/>
+      <c r="P239" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q239" t="n">
+        <v>236.8</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -14606,6 +16040,12 @@
       </c>
       <c r="N240" t="inlineStr"/>
       <c r="O240" t="inlineStr"/>
+      <c r="P240" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q240" t="n">
+        <v>627.15</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -14669,6 +16109,12 @@
       </c>
       <c r="N241" t="inlineStr"/>
       <c r="O241" t="inlineStr"/>
+      <c r="P241" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q241" t="n">
+        <v>4245.75</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -14720,6 +16166,12 @@
           <t>Core/T2_MediumVolume</t>
         </is>
       </c>
+      <c r="P242" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q242" t="n">
+        <v>46213</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -14771,6 +16223,12 @@
       </c>
       <c r="N243" t="inlineStr"/>
       <c r="O243" t="inlineStr"/>
+      <c r="P243" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q243" t="n">
+        <v>2434.6</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -14834,6 +16292,12 @@
       </c>
       <c r="N244" t="inlineStr"/>
       <c r="O244" t="inlineStr"/>
+      <c r="P244" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q244" t="n">
+        <v>2434.6</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -14885,6 +16349,12 @@
       </c>
       <c r="N245" t="inlineStr"/>
       <c r="O245" t="inlineStr"/>
+      <c r="P245" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q245" t="n">
+        <v>5109.7</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -14948,6 +16418,12 @@
       </c>
       <c r="N246" t="inlineStr"/>
       <c r="O246" t="inlineStr"/>
+      <c r="P246" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q246" t="n">
+        <v>471.75</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -15011,6 +16487,12 @@
       </c>
       <c r="N247" t="inlineStr"/>
       <c r="O247" t="inlineStr"/>
+      <c r="P247" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q247" t="n">
+        <v>236.8</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -15074,6 +16556,12 @@
       </c>
       <c r="N248" t="inlineStr"/>
       <c r="O248" t="inlineStr"/>
+      <c r="P248" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q248" t="n">
+        <v>627.15</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -15137,6 +16625,12 @@
       </c>
       <c r="N249" t="inlineStr"/>
       <c r="O249" t="inlineStr"/>
+      <c r="P249" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q249" t="n">
+        <v>3774</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -15188,6 +16682,12 @@
       </c>
       <c r="N250" t="inlineStr"/>
       <c r="O250" t="inlineStr"/>
+      <c r="P250" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q250" t="n">
+        <v>5109.7</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -15251,6 +16751,12 @@
       </c>
       <c r="N251" t="inlineStr"/>
       <c r="O251" t="inlineStr"/>
+      <c r="P251" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q251" t="n">
+        <v>471.75</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -15314,6 +16820,12 @@
       </c>
       <c r="N252" t="inlineStr"/>
       <c r="O252" t="inlineStr"/>
+      <c r="P252" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q252" t="n">
+        <v>236.8</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -15377,6 +16889,12 @@
       </c>
       <c r="N253" t="inlineStr"/>
       <c r="O253" t="inlineStr"/>
+      <c r="P253" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q253" t="n">
+        <v>627.15</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -15440,6 +16958,12 @@
       </c>
       <c r="N254" t="inlineStr"/>
       <c r="O254" t="inlineStr"/>
+      <c r="P254" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q254" t="n">
+        <v>3774</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -15491,6 +17015,12 @@
       </c>
       <c r="N255" t="inlineStr"/>
       <c r="O255" t="inlineStr"/>
+      <c r="P255" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q255" t="n">
+        <v>6053.2</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -15554,6 +17084,12 @@
       </c>
       <c r="N256" t="inlineStr"/>
       <c r="O256" t="inlineStr"/>
+      <c r="P256" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q256" t="n">
+        <v>236.8</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -15617,6 +17153,12 @@
       </c>
       <c r="N257" t="inlineStr"/>
       <c r="O257" t="inlineStr"/>
+      <c r="P257" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q257" t="n">
+        <v>784.4</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -15680,6 +17222,12 @@
       </c>
       <c r="N258" t="inlineStr"/>
       <c r="O258" t="inlineStr"/>
+      <c r="P258" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q258" t="n">
+        <v>5032</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -15731,6 +17279,12 @@
       </c>
       <c r="N259" t="inlineStr"/>
       <c r="O259" t="inlineStr"/>
+      <c r="P259" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q259" t="n">
+        <v>4243.9</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -15794,6 +17348,12 @@
       </c>
       <c r="N260" t="inlineStr"/>
       <c r="O260" t="inlineStr"/>
+      <c r="P260" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q260" t="n">
+        <v>236.8</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -15857,6 +17417,12 @@
       </c>
       <c r="N261" t="inlineStr"/>
       <c r="O261" t="inlineStr"/>
+      <c r="P261" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q261" t="n">
+        <v>627.15</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -15920,6 +17486,12 @@
       </c>
       <c r="N262" t="inlineStr"/>
       <c r="O262" t="inlineStr"/>
+      <c r="P262" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q262" t="n">
+        <v>3379.95</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -15971,6 +17543,12 @@
       </c>
       <c r="N263" t="inlineStr"/>
       <c r="O263" t="inlineStr"/>
+      <c r="P263" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q263" t="n">
+        <v>4243.9</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -16034,6 +17612,12 @@
       </c>
       <c r="N264" t="inlineStr"/>
       <c r="O264" t="inlineStr"/>
+      <c r="P264" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q264" t="n">
+        <v>236.8</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -16097,6 +17681,12 @@
       </c>
       <c r="N265" t="inlineStr"/>
       <c r="O265" t="inlineStr"/>
+      <c r="P265" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q265" t="n">
+        <v>627.15</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -16160,6 +17750,12 @@
       </c>
       <c r="N266" t="inlineStr"/>
       <c r="O266" t="inlineStr"/>
+      <c r="P266" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q266" t="n">
+        <v>3379.95</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -16211,6 +17807,12 @@
       </c>
       <c r="N267" t="inlineStr"/>
       <c r="O267" t="inlineStr"/>
+      <c r="P267" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q267" t="n">
+        <v>4243.9</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -16274,6 +17876,12 @@
       </c>
       <c r="N268" t="inlineStr"/>
       <c r="O268" t="inlineStr"/>
+      <c r="P268" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q268" t="n">
+        <v>236.8</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -16337,6 +17945,12 @@
       </c>
       <c r="N269" t="inlineStr"/>
       <c r="O269" t="inlineStr"/>
+      <c r="P269" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q269" t="n">
+        <v>627.15</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -16400,6 +18014,12 @@
       </c>
       <c r="N270" t="inlineStr"/>
       <c r="O270" t="inlineStr"/>
+      <c r="P270" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q270" t="n">
+        <v>3379.95</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -16451,6 +18071,12 @@
       </c>
       <c r="N271" t="inlineStr"/>
       <c r="O271" t="inlineStr"/>
+      <c r="P271" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q271" t="n">
+        <v>4558.4</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -16514,6 +18140,12 @@
       </c>
       <c r="N272" t="inlineStr"/>
       <c r="O272" t="inlineStr"/>
+      <c r="P272" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q272" t="n">
+        <v>236.8</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -16577,6 +18209,12 @@
       </c>
       <c r="N273" t="inlineStr"/>
       <c r="O273" t="inlineStr"/>
+      <c r="P273" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q273" t="n">
+        <v>627.15</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -16640,6 +18278,12 @@
       </c>
       <c r="N274" t="inlineStr"/>
       <c r="O274" t="inlineStr"/>
+      <c r="P274" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q274" t="n">
+        <v>3694.45</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -16691,6 +18335,12 @@
       </c>
       <c r="N275" t="inlineStr"/>
       <c r="O275" t="inlineStr"/>
+      <c r="P275" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q275" t="n">
+        <v>3379.95</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -16754,6 +18404,12 @@
       </c>
       <c r="N276" t="inlineStr"/>
       <c r="O276" t="inlineStr"/>
+      <c r="P276" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q276" t="n">
+        <v>236.8</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -16817,6 +18473,12 @@
       </c>
       <c r="N277" t="inlineStr"/>
       <c r="O277" t="inlineStr"/>
+      <c r="P277" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q277" t="n">
+        <v>627.15</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -16880,6 +18542,12 @@
       </c>
       <c r="N278" t="inlineStr"/>
       <c r="O278" t="inlineStr"/>
+      <c r="P278" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q278" t="n">
+        <v>2516</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -16931,6 +18599,12 @@
       </c>
       <c r="N279" t="inlineStr"/>
       <c r="O279" t="inlineStr"/>
+      <c r="P279" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q279" t="n">
+        <v>4008.95</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -16994,6 +18668,12 @@
       </c>
       <c r="N280" t="inlineStr"/>
       <c r="O280" t="inlineStr"/>
+      <c r="P280" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q280" t="n">
+        <v>236.8</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -17057,6 +18737,12 @@
       </c>
       <c r="N281" t="inlineStr"/>
       <c r="O281" t="inlineStr"/>
+      <c r="P281" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q281" t="n">
+        <v>627.15</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -17120,6 +18806,12 @@
       </c>
       <c r="N282" t="inlineStr"/>
       <c r="O282" t="inlineStr"/>
+      <c r="P282" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q282" t="n">
+        <v>3145</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -17171,6 +18863,12 @@
       </c>
       <c r="N283" t="inlineStr"/>
       <c r="O283" t="inlineStr"/>
+      <c r="P283" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q283" t="n">
+        <v>2826.8</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -17234,6 +18932,12 @@
       </c>
       <c r="N284" t="inlineStr"/>
       <c r="O284" t="inlineStr"/>
+      <c r="P284" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q284" t="n">
+        <v>2826.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17246,7 +18950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O284"/>
+  <dimension ref="A1:Q284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17323,6 +19027,16 @@
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Rate_USD</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Price_USD</t>
         </is>
       </c>
     </row>
@@ -17360,6 +19074,8 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17407,6 +19123,12 @@
           <t>Advanced/T1_LargeVolume</t>
         </is>
       </c>
+      <c r="P3" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>64333.75</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -17458,6 +19180,12 @@
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>14189.5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -17521,6 +19249,12 @@
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>481</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17584,6 +19318,12 @@
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1202.5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17647,6 +19387,12 @@
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>12506</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17698,6 +19444,12 @@
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4810</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17761,6 +19513,12 @@
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4810</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17812,6 +19570,12 @@
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4810</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -17875,6 +19639,12 @@
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4810</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -17926,6 +19696,12 @@
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>12145.25</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -17989,6 +19765,12 @@
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>962</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -18052,6 +19834,12 @@
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1563.25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18115,6 +19903,12 @@
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>9620</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -18166,6 +19960,12 @@
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>12145.25</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -18229,6 +20029,12 @@
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
+      <c r="P17" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>962</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -18292,6 +20098,12 @@
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
+      <c r="P18" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1563.25</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -18355,6 +20167,12 @@
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>9620</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -18406,6 +20224,12 @@
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1924</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -18469,6 +20293,12 @@
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
+      <c r="P21" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -18532,6 +20362,12 @@
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1202.5</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -18583,6 +20419,12 @@
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1924</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -18646,6 +20488,12 @@
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -18709,6 +20557,12 @@
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
+      <c r="P25" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1202.5</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -18760,6 +20614,12 @@
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
+      <c r="P26" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1322.75</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -18823,6 +20683,12 @@
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
+      <c r="P27" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -18886,6 +20752,12 @@
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>601.25</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -18937,6 +20809,12 @@
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1924</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -19000,6 +20878,12 @@
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -19063,6 +20947,12 @@
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1202.5</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -19114,6 +21004,12 @@
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
+      <c r="P32" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1924</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -19177,6 +21073,12 @@
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
+      <c r="P33" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -19240,6 +21142,12 @@
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
+      <c r="P34" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1202.5</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -19291,6 +21199,12 @@
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
+      <c r="P35" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1322.75</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -19354,6 +21268,12 @@
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
+      <c r="P36" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -19417,6 +21337,12 @@
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
+      <c r="P37" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>601.25</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -19468,6 +21394,12 @@
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
+      <c r="P38" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1322.75</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -19531,6 +21463,12 @@
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
+      <c r="P39" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1322.75</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -19582,6 +21520,12 @@
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
+      <c r="P40" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1322.75</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -19645,6 +21589,12 @@
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
+      <c r="P41" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -19708,6 +21658,12 @@
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
+      <c r="P42" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>601.25</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -19759,6 +21715,12 @@
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
+      <c r="P43" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1322.75</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -19822,6 +21784,12 @@
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
+      <c r="P44" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -19885,6 +21853,12 @@
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
+      <c r="P45" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>601.25</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -19936,6 +21910,12 @@
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
+      <c r="P46" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1924</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -19999,6 +21979,12 @@
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
+      <c r="P47" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -20062,6 +22048,12 @@
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
+      <c r="P48" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1202.5</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -20113,6 +22105,12 @@
           <t>Advanced/T1_LargeVolume</t>
         </is>
       </c>
+      <c r="P49" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>53335.5</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -20164,6 +22162,12 @@
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
+      <c r="P50" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>601.25</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -20227,6 +22231,12 @@
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
+      <c r="P51" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>240.5</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -20290,6 +22300,12 @@
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
+      <c r="P52" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>360.75</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -20341,6 +22357,12 @@
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
+      <c r="P53" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>1322.75</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -20404,6 +22426,12 @@
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
+      <c r="P54" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>360.75</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -20467,6 +22495,12 @@
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
+      <c r="P55" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>962</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -20518,6 +22552,12 @@
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
+      <c r="P56" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>4810</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -20581,6 +22621,12 @@
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
+      <c r="P57" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>4810</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -20632,6 +22678,12 @@
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
+      <c r="P58" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>7215</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -20695,6 +22747,12 @@
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
+      <c r="P59" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>7215</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -20746,6 +22804,12 @@
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
+      <c r="P60" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>4750.8</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -20809,6 +22873,12 @@
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
+      <c r="P61" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>2405</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -20872,6 +22942,12 @@
       </c>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
+      <c r="P62" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>601.25</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -20935,6 +23011,12 @@
       </c>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
+      <c r="P63" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>421.8</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -20998,6 +23080,12 @@
       </c>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
+      <c r="P64" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -21061,6 +23149,12 @@
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
+      <c r="P65" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>601.25</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -21112,6 +23206,12 @@
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
+      <c r="P66" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>4810</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -21175,6 +23275,12 @@
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
+      <c r="P67" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>4810</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -21226,6 +23332,12 @@
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
+      <c r="P68" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>3246.75</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -21289,6 +23401,12 @@
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
+      <c r="P69" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>3246.75</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -21340,6 +23458,12 @@
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
+      <c r="P70" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>3246.75</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -21403,6 +23527,12 @@
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
+      <c r="P71" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>3246.75</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -21454,6 +23584,12 @@
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
+      <c r="P72" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>2947.05</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -21517,6 +23653,12 @@
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
+      <c r="P73" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>1202.5</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -21580,6 +23722,12 @@
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
+      <c r="P74" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>421.8</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -21643,6 +23791,12 @@
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
+      <c r="P75" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -21706,6 +23860,12 @@
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
+      <c r="P76" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>601.25</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -21757,6 +23917,12 @@
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
+      <c r="P77" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>2947.05</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -21820,6 +23986,12 @@
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
+      <c r="P78" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>1202.5</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -21883,6 +24055,12 @@
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
+      <c r="P79" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>421.8</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -21946,6 +24124,12 @@
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
+      <c r="P80" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -22009,6 +24193,12 @@
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
+      <c r="P81" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>601.25</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -22060,6 +24250,12 @@
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
+      <c r="P82" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>2405</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -22123,6 +24319,12 @@
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
+      <c r="P83" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>2405</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -22174,6 +24376,12 @@
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
+      <c r="P84" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>841.75</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -22237,6 +24445,12 @@
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
+      <c r="P85" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>841.75</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -22288,6 +24502,12 @@
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
+      <c r="P86" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>1924</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -22351,6 +24571,12 @@
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
+      <c r="P87" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -22414,6 +24640,12 @@
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
+      <c r="P88" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>1202.5</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -22465,6 +24697,12 @@
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
+      <c r="P89" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>2706.55</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -22528,6 +24766,12 @@
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
+      <c r="P90" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>240.5</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -22591,6 +24835,12 @@
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
+      <c r="P91" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>421.8</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -22654,6 +24904,12 @@
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
+      <c r="P92" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -22717,6 +24973,12 @@
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
+      <c r="P93" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>1322.75</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -22768,6 +25030,12 @@
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
+      <c r="P94" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>3187.55</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -22831,6 +25099,12 @@
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
+      <c r="P95" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>421.8</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -22894,6 +25168,12 @@
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
+      <c r="P96" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -22957,6 +25237,12 @@
       </c>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
+      <c r="P97" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>2044.25</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -23008,6 +25294,12 @@
       </c>
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
+      <c r="P98" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>1082.25</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -23071,6 +25363,12 @@
       </c>
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr"/>
+      <c r="P99" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>1082.25</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -23122,6 +25420,12 @@
       </c>
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr"/>
+      <c r="P100" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>962</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -23185,6 +25489,12 @@
       </c>
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr"/>
+      <c r="P101" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -23248,6 +25558,12 @@
       </c>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr"/>
+      <c r="P102" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>240.5</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -23299,6 +25615,12 @@
       </c>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr"/>
+      <c r="P103" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>481</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -23362,6 +25684,12 @@
       </c>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
+      <c r="P104" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>481</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -23413,6 +25741,12 @@
       </c>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
+      <c r="P105" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>481</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -23476,6 +25810,12 @@
       </c>
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr"/>
+      <c r="P106" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>481</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -23527,6 +25867,12 @@
       </c>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
+      <c r="P107" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>481</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -23590,6 +25936,12 @@
       </c>
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr"/>
+      <c r="P108" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>481</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -23641,6 +25993,12 @@
       </c>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
+      <c r="P109" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>1443</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -23704,6 +26062,12 @@
       </c>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr"/>
+      <c r="P110" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>1443</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -23755,6 +26119,12 @@
       </c>
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr"/>
+      <c r="P111" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>1443</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -23818,6 +26188,12 @@
       </c>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
+      <c r="P112" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>1443</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -23869,6 +26245,12 @@
           <t>Advanced/T1_LargeVolume</t>
         </is>
       </c>
+      <c r="P113" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>112084.1</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -23920,6 +26302,12 @@
       </c>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr"/>
+      <c r="P114" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>3428.05</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -23983,6 +26371,12 @@
       </c>
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr"/>
+      <c r="P115" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -24046,6 +26440,12 @@
       </c>
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr"/>
+      <c r="P116" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>421.8</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -24109,6 +26509,12 @@
       </c>
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr"/>
+      <c r="P117" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -24172,6 +26578,12 @@
       </c>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
+      <c r="P118" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>1563.25</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -24223,6 +26635,12 @@
       </c>
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr"/>
+      <c r="P119" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>7276.05</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -24286,6 +26704,12 @@
       </c>
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
+      <c r="P120" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>5772</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -24349,6 +26773,12 @@
       </c>
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr"/>
+      <c r="P121" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>360.75</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -24412,6 +26842,12 @@
       </c>
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
+      <c r="P122" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>421.8</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -24475,6 +26911,12 @@
       </c>
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr"/>
+      <c r="P123" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -24526,6 +26968,12 @@
       </c>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
+      <c r="P124" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>3307.8</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -24589,6 +27037,12 @@
       </c>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr"/>
+      <c r="P125" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -24652,6 +27106,12 @@
       </c>
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr"/>
+      <c r="P126" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>421.8</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -24715,6 +27175,12 @@
       </c>
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr"/>
+      <c r="P127" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -24778,6 +27244,12 @@
       </c>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr"/>
+      <c r="P128" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>1443</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -24829,6 +27301,12 @@
       </c>
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr"/>
+      <c r="P129" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>4689.75</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -24892,6 +27370,12 @@
       </c>
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr"/>
+      <c r="P130" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>4689.75</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -24943,6 +27427,12 @@
       </c>
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr"/>
+      <c r="P131" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>4689.75</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -25006,6 +27496,12 @@
       </c>
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr"/>
+      <c r="P132" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>4689.75</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -25057,6 +27553,12 @@
       </c>
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr"/>
+      <c r="P133" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>6493.5</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -25120,6 +27622,12 @@
       </c>
       <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr"/>
+      <c r="P134" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>6493.5</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -25171,6 +27679,12 @@
       </c>
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr"/>
+      <c r="P135" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>8658</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -25234,6 +27748,12 @@
       </c>
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr"/>
+      <c r="P136" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>8658</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -25285,6 +27805,12 @@
       </c>
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
+      <c r="P137" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>3367</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -25348,6 +27874,12 @@
       </c>
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr"/>
+      <c r="P138" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -25411,6 +27943,12 @@
       </c>
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr"/>
+      <c r="P139" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -25474,6 +28012,12 @@
       </c>
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
+      <c r="P140" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>1924</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -25525,6 +28069,12 @@
       </c>
       <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr"/>
+      <c r="P141" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>5772</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -25588,6 +28138,12 @@
       </c>
       <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr"/>
+      <c r="P142" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>5772</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -25639,6 +28195,12 @@
       </c>
       <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr"/>
+      <c r="P143" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>1082.25</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -25702,6 +28264,12 @@
       </c>
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr"/>
+      <c r="P144" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>1082.25</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -25753,6 +28321,12 @@
       </c>
       <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr"/>
+      <c r="P145" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>4329</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -25816,6 +28390,12 @@
       </c>
       <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr"/>
+      <c r="P146" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>4329</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -25867,6 +28447,12 @@
       </c>
       <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr"/>
+      <c r="P147" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>3607.5</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -25930,6 +28516,12 @@
       </c>
       <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr"/>
+      <c r="P148" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>3607.5</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -25981,6 +28573,12 @@
       </c>
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr"/>
+      <c r="P149" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>7094.75</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -26044,6 +28642,12 @@
       </c>
       <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr"/>
+      <c r="P150" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>7094.75</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -26095,6 +28699,12 @@
       </c>
       <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr"/>
+      <c r="P151" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>6974.5</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -26158,6 +28768,12 @@
       </c>
       <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr"/>
+      <c r="P152" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>6974.5</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -26209,6 +28825,12 @@
       </c>
       <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr"/>
+      <c r="P153" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>6073.55</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -26272,6 +28894,12 @@
       </c>
       <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr"/>
+      <c r="P154" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>2886</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -26335,6 +28963,12 @@
       </c>
       <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr"/>
+      <c r="P155" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>421.8</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -26398,6 +29032,12 @@
       </c>
       <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr"/>
+      <c r="P156" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>1082.25</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -26461,6 +29101,12 @@
       </c>
       <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr"/>
+      <c r="P157" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>1683.5</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -26512,6 +29158,12 @@
       </c>
       <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr"/>
+      <c r="P158" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>4750.8</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -26575,6 +29227,12 @@
       </c>
       <c r="N159" t="inlineStr"/>
       <c r="O159" t="inlineStr"/>
+      <c r="P159" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>3367</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -26638,6 +29296,12 @@
       </c>
       <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr"/>
+      <c r="P160" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>421.8</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -26701,6 +29365,12 @@
       </c>
       <c r="N161" t="inlineStr"/>
       <c r="O161" t="inlineStr"/>
+      <c r="P161" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>962</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -26752,6 +29422,12 @@
       </c>
       <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr"/>
+      <c r="P162" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>2706.55</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -26815,6 +29491,12 @@
       </c>
       <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr"/>
+      <c r="P163" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>240.5</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -26878,6 +29560,12 @@
       </c>
       <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr"/>
+      <c r="P164" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>421.8</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -26941,6 +29629,12 @@
       </c>
       <c r="N165" t="inlineStr"/>
       <c r="O165" t="inlineStr"/>
+      <c r="P165" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -27004,6 +29698,12 @@
       </c>
       <c r="N166" t="inlineStr"/>
       <c r="O166" t="inlineStr"/>
+      <c r="P166" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>1322.75</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -27055,6 +29755,12 @@
       </c>
       <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr"/>
+      <c r="P167" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>962</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -27118,6 +29824,12 @@
       </c>
       <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr"/>
+      <c r="P168" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>240.5</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -27181,6 +29893,12 @@
       </c>
       <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr"/>
+      <c r="P169" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -27232,6 +29950,12 @@
       </c>
       <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr"/>
+      <c r="P170" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>3788.8</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -27295,6 +30019,12 @@
       </c>
       <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr"/>
+      <c r="P171" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>2645.5</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -27358,6 +30088,12 @@
       </c>
       <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr"/>
+      <c r="P172" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>421.8</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -27421,6 +30157,12 @@
       </c>
       <c r="N173" t="inlineStr"/>
       <c r="O173" t="inlineStr"/>
+      <c r="P173" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -27472,6 +30214,12 @@
       </c>
       <c r="N174" t="inlineStr"/>
       <c r="O174" t="inlineStr"/>
+      <c r="P174" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>5472.3</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -27535,6 +30283,12 @@
       </c>
       <c r="N175" t="inlineStr"/>
       <c r="O175" t="inlineStr"/>
+      <c r="P175" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>421.8</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -27598,6 +30352,12 @@
       </c>
       <c r="N176" t="inlineStr"/>
       <c r="O176" t="inlineStr"/>
+      <c r="P176" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -27661,6 +30421,12 @@
       </c>
       <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr"/>
+      <c r="P177" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>1563.25</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -27724,6 +30490,12 @@
       </c>
       <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr"/>
+      <c r="P178" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>2765.75</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -27775,6 +30547,12 @@
       </c>
       <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr"/>
+      <c r="P179" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>5953.3</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -27838,6 +30616,12 @@
       </c>
       <c r="N180" t="inlineStr"/>
       <c r="O180" t="inlineStr"/>
+      <c r="P180" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>421.8</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -27901,6 +30685,12 @@
       </c>
       <c r="N181" t="inlineStr"/>
       <c r="O181" t="inlineStr"/>
+      <c r="P181" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>962</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -27964,6 +30754,12 @@
       </c>
       <c r="N182" t="inlineStr"/>
       <c r="O182" t="inlineStr"/>
+      <c r="P182" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>4569.5</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -28015,6 +30811,12 @@
       </c>
       <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr"/>
+      <c r="P183" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>3548.3</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -28078,6 +30880,12 @@
       </c>
       <c r="N184" t="inlineStr"/>
       <c r="O184" t="inlineStr"/>
+      <c r="P184" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>421.8</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -28141,6 +30949,12 @@
       </c>
       <c r="N185" t="inlineStr"/>
       <c r="O185" t="inlineStr"/>
+      <c r="P185" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>1082.25</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -28204,6 +31018,12 @@
       </c>
       <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr"/>
+      <c r="P186" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>2044.25</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -28255,6 +31075,12 @@
       </c>
       <c r="N187" t="inlineStr"/>
       <c r="O187" t="inlineStr"/>
+      <c r="P187" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>2826.8</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -28318,6 +31144,12 @@
       </c>
       <c r="N188" t="inlineStr"/>
       <c r="O188" t="inlineStr"/>
+      <c r="P188" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>421.8</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -28381,6 +31213,12 @@
       </c>
       <c r="N189" t="inlineStr"/>
       <c r="O189" t="inlineStr"/>
+      <c r="P189" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -28444,6 +31282,12 @@
       </c>
       <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr"/>
+      <c r="P190" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>1683.5</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -28495,6 +31339,12 @@
       </c>
       <c r="N191" t="inlineStr"/>
       <c r="O191" t="inlineStr"/>
+      <c r="P191" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>3788.8</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -28558,6 +31408,12 @@
       </c>
       <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr"/>
+      <c r="P192" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>421.8</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -28621,6 +31477,12 @@
       </c>
       <c r="N193" t="inlineStr"/>
       <c r="O193" t="inlineStr"/>
+      <c r="P193" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -28684,6 +31546,12 @@
       </c>
       <c r="N194" t="inlineStr"/>
       <c r="O194" t="inlineStr"/>
+      <c r="P194" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -28747,6 +31615,12 @@
       </c>
       <c r="N195" t="inlineStr"/>
       <c r="O195" t="inlineStr"/>
+      <c r="P195" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q195" t="n">
+        <v>1924</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -28798,6 +31672,12 @@
       </c>
       <c r="N196" t="inlineStr"/>
       <c r="O196" t="inlineStr"/>
+      <c r="P196" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>1082.25</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -28861,6 +31741,12 @@
       </c>
       <c r="N197" t="inlineStr"/>
       <c r="O197" t="inlineStr"/>
+      <c r="P197" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q197" t="n">
+        <v>1082.25</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -28912,6 +31798,12 @@
       </c>
       <c r="N198" t="inlineStr"/>
       <c r="O198" t="inlineStr"/>
+      <c r="P198" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q198" t="n">
+        <v>360.75</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -28975,6 +31867,12 @@
       </c>
       <c r="N199" t="inlineStr"/>
       <c r="O199" t="inlineStr"/>
+      <c r="P199" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>360.75</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -29026,6 +31924,12 @@
           <t>Advanced/T1_LargeVolume</t>
         </is>
       </c>
+      <c r="P200" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>72286.89999999999</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -29077,6 +31981,12 @@
       </c>
       <c r="N201" t="inlineStr"/>
       <c r="O201" t="inlineStr"/>
+      <c r="P201" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>4329</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -29140,6 +32050,12 @@
       </c>
       <c r="N202" t="inlineStr"/>
       <c r="O202" t="inlineStr"/>
+      <c r="P202" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>4329</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -29191,6 +32107,12 @@
       </c>
       <c r="N203" t="inlineStr"/>
       <c r="O203" t="inlineStr"/>
+      <c r="P203" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>7096.6</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -29254,6 +32176,12 @@
       </c>
       <c r="N204" t="inlineStr"/>
       <c r="O204" t="inlineStr"/>
+      <c r="P204" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>1202.5</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -29317,6 +32245,12 @@
       </c>
       <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr"/>
+      <c r="P205" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q205" t="n">
+        <v>362.6</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -29380,6 +32314,12 @@
       </c>
       <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr"/>
+      <c r="P206" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>962</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -29443,6 +32383,12 @@
       </c>
       <c r="N207" t="inlineStr"/>
       <c r="O207" t="inlineStr"/>
+      <c r="P207" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>4569.5</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -29494,6 +32440,12 @@
       </c>
       <c r="N208" t="inlineStr"/>
       <c r="O208" t="inlineStr"/>
+      <c r="P208" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>10463.6</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -29557,6 +32509,12 @@
       </c>
       <c r="N209" t="inlineStr"/>
       <c r="O209" t="inlineStr"/>
+      <c r="P209" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -29620,6 +32578,12 @@
       </c>
       <c r="N210" t="inlineStr"/>
       <c r="O210" t="inlineStr"/>
+      <c r="P210" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>362.6</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -29683,6 +32647,12 @@
       </c>
       <c r="N211" t="inlineStr"/>
       <c r="O211" t="inlineStr"/>
+      <c r="P211" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>962</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -29746,6 +32716,12 @@
       </c>
       <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr"/>
+      <c r="P212" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>8417.5</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -29797,6 +32773,12 @@
       </c>
       <c r="N213" t="inlineStr"/>
       <c r="O213" t="inlineStr"/>
+      <c r="P213" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>9742.1</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -29860,6 +32842,12 @@
       </c>
       <c r="N214" t="inlineStr"/>
       <c r="O214" t="inlineStr"/>
+      <c r="P214" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -29923,6 +32911,12 @@
       </c>
       <c r="N215" t="inlineStr"/>
       <c r="O215" t="inlineStr"/>
+      <c r="P215" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>362.6</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -29986,6 +32980,12 @@
       </c>
       <c r="N216" t="inlineStr"/>
       <c r="O216" t="inlineStr"/>
+      <c r="P216" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>962</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -30049,6 +33049,12 @@
       </c>
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr"/>
+      <c r="P217" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>7696</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -30100,6 +33106,12 @@
       </c>
       <c r="N218" t="inlineStr"/>
       <c r="O218" t="inlineStr"/>
+      <c r="P218" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q218" t="n">
+        <v>6615.6</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -30163,6 +33175,12 @@
       </c>
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr"/>
+      <c r="P219" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>362.6</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -30226,6 +33244,12 @@
       </c>
       <c r="N220" t="inlineStr"/>
       <c r="O220" t="inlineStr"/>
+      <c r="P220" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>1202.5</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -30289,6 +33313,12 @@
       </c>
       <c r="N221" t="inlineStr"/>
       <c r="O221" t="inlineStr"/>
+      <c r="P221" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>5050.5</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -30340,6 +33370,12 @@
       </c>
       <c r="N222" t="inlineStr"/>
       <c r="O222" t="inlineStr"/>
+      <c r="P222" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>7577.6</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -30403,6 +33439,12 @@
       </c>
       <c r="N223" t="inlineStr"/>
       <c r="O223" t="inlineStr"/>
+      <c r="P223" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>362.6</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -30466,6 +33508,12 @@
       </c>
       <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr"/>
+      <c r="P224" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>962</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -30529,6 +33577,12 @@
       </c>
       <c r="N225" t="inlineStr"/>
       <c r="O225" t="inlineStr"/>
+      <c r="P225" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>6253</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -30580,6 +33634,12 @@
       </c>
       <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr"/>
+      <c r="P226" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>6375.1</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -30643,6 +33703,12 @@
       </c>
       <c r="N227" t="inlineStr"/>
       <c r="O227" t="inlineStr"/>
+      <c r="P227" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>362.6</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -30706,6 +33772,12 @@
       </c>
       <c r="N228" t="inlineStr"/>
       <c r="O228" t="inlineStr"/>
+      <c r="P228" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q228" t="n">
+        <v>962</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -30769,6 +33841,12 @@
       </c>
       <c r="N229" t="inlineStr"/>
       <c r="O229" t="inlineStr"/>
+      <c r="P229" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q229" t="n">
+        <v>5050.5</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -30820,6 +33898,12 @@
       </c>
       <c r="N230" t="inlineStr"/>
       <c r="O230" t="inlineStr"/>
+      <c r="P230" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q230" t="n">
+        <v>5172.6</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -30883,6 +33967,12 @@
       </c>
       <c r="N231" t="inlineStr"/>
       <c r="O231" t="inlineStr"/>
+      <c r="P231" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q231" t="n">
+        <v>362.6</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -30946,6 +34036,12 @@
       </c>
       <c r="N232" t="inlineStr"/>
       <c r="O232" t="inlineStr"/>
+      <c r="P232" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q232" t="n">
+        <v>1202.5</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -31009,6 +34105,12 @@
       </c>
       <c r="N233" t="inlineStr"/>
       <c r="O233" t="inlineStr"/>
+      <c r="P233" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>3607.5</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -31060,6 +34162,12 @@
       </c>
       <c r="N234" t="inlineStr"/>
       <c r="O234" t="inlineStr"/>
+      <c r="P234" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q234" t="n">
+        <v>7096.6</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -31123,6 +34231,12 @@
       </c>
       <c r="N235" t="inlineStr"/>
       <c r="O235" t="inlineStr"/>
+      <c r="P235" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q235" t="n">
+        <v>362.6</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -31186,6 +34300,12 @@
       </c>
       <c r="N236" t="inlineStr"/>
       <c r="O236" t="inlineStr"/>
+      <c r="P236" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q236" t="n">
+        <v>962</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -31249,6 +34369,12 @@
       </c>
       <c r="N237" t="inlineStr"/>
       <c r="O237" t="inlineStr"/>
+      <c r="P237" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q237" t="n">
+        <v>5772</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -31300,6 +34426,12 @@
       </c>
       <c r="N238" t="inlineStr"/>
       <c r="O238" t="inlineStr"/>
+      <c r="P238" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q238" t="n">
+        <v>7818.1</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -31363,6 +34495,12 @@
       </c>
       <c r="N239" t="inlineStr"/>
       <c r="O239" t="inlineStr"/>
+      <c r="P239" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q239" t="n">
+        <v>362.6</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -31426,6 +34564,12 @@
       </c>
       <c r="N240" t="inlineStr"/>
       <c r="O240" t="inlineStr"/>
+      <c r="P240" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q240" t="n">
+        <v>962</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -31489,6 +34633,12 @@
       </c>
       <c r="N241" t="inlineStr"/>
       <c r="O241" t="inlineStr"/>
+      <c r="P241" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q241" t="n">
+        <v>6493.5</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -31540,6 +34690,12 @@
           <t>Advanced/T1_LargeVolume</t>
         </is>
       </c>
+      <c r="P242" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q242" t="n">
+        <v>70723.64999999999</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -31591,6 +34747,12 @@
       </c>
       <c r="N243" t="inlineStr"/>
       <c r="O243" t="inlineStr"/>
+      <c r="P243" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q243" t="n">
+        <v>3727.75</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -31654,6 +34816,12 @@
       </c>
       <c r="N244" t="inlineStr"/>
       <c r="O244" t="inlineStr"/>
+      <c r="P244" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q244" t="n">
+        <v>3727.75</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -31705,6 +34873,12 @@
       </c>
       <c r="N245" t="inlineStr"/>
       <c r="O245" t="inlineStr"/>
+      <c r="P245" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q245" t="n">
+        <v>7818.1</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -31768,6 +34942,12 @@
       </c>
       <c r="N246" t="inlineStr"/>
       <c r="O246" t="inlineStr"/>
+      <c r="P246" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q246" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -31831,6 +35011,12 @@
       </c>
       <c r="N247" t="inlineStr"/>
       <c r="O247" t="inlineStr"/>
+      <c r="P247" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q247" t="n">
+        <v>362.6</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -31894,6 +35080,12 @@
       </c>
       <c r="N248" t="inlineStr"/>
       <c r="O248" t="inlineStr"/>
+      <c r="P248" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q248" t="n">
+        <v>962</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -31957,6 +35149,12 @@
       </c>
       <c r="N249" t="inlineStr"/>
       <c r="O249" t="inlineStr"/>
+      <c r="P249" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q249" t="n">
+        <v>5772</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -32008,6 +35206,12 @@
       </c>
       <c r="N250" t="inlineStr"/>
       <c r="O250" t="inlineStr"/>
+      <c r="P250" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q250" t="n">
+        <v>7818.1</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -32071,6 +35275,12 @@
       </c>
       <c r="N251" t="inlineStr"/>
       <c r="O251" t="inlineStr"/>
+      <c r="P251" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q251" t="n">
+        <v>721.5</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -32134,6 +35344,12 @@
       </c>
       <c r="N252" t="inlineStr"/>
       <c r="O252" t="inlineStr"/>
+      <c r="P252" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q252" t="n">
+        <v>362.6</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -32197,6 +35413,12 @@
       </c>
       <c r="N253" t="inlineStr"/>
       <c r="O253" t="inlineStr"/>
+      <c r="P253" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q253" t="n">
+        <v>962</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -32260,6 +35482,12 @@
       </c>
       <c r="N254" t="inlineStr"/>
       <c r="O254" t="inlineStr"/>
+      <c r="P254" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q254" t="n">
+        <v>5772</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -32311,6 +35539,12 @@
       </c>
       <c r="N255" t="inlineStr"/>
       <c r="O255" t="inlineStr"/>
+      <c r="P255" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q255" t="n">
+        <v>9261.1</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -32374,6 +35608,12 @@
       </c>
       <c r="N256" t="inlineStr"/>
       <c r="O256" t="inlineStr"/>
+      <c r="P256" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q256" t="n">
+        <v>362.6</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -32437,6 +35677,12 @@
       </c>
       <c r="N257" t="inlineStr"/>
       <c r="O257" t="inlineStr"/>
+      <c r="P257" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q257" t="n">
+        <v>1202.5</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -32500,6 +35746,12 @@
       </c>
       <c r="N258" t="inlineStr"/>
       <c r="O258" t="inlineStr"/>
+      <c r="P258" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q258" t="n">
+        <v>7696</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -32551,6 +35803,12 @@
       </c>
       <c r="N259" t="inlineStr"/>
       <c r="O259" t="inlineStr"/>
+      <c r="P259" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q259" t="n">
+        <v>6495.35</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -32614,6 +35872,12 @@
       </c>
       <c r="N260" t="inlineStr"/>
       <c r="O260" t="inlineStr"/>
+      <c r="P260" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q260" t="n">
+        <v>362.6</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -32677,6 +35941,12 @@
       </c>
       <c r="N261" t="inlineStr"/>
       <c r="O261" t="inlineStr"/>
+      <c r="P261" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q261" t="n">
+        <v>962</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -32740,6 +36010,12 @@
       </c>
       <c r="N262" t="inlineStr"/>
       <c r="O262" t="inlineStr"/>
+      <c r="P262" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q262" t="n">
+        <v>5170.75</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -32791,6 +36067,12 @@
       </c>
       <c r="N263" t="inlineStr"/>
       <c r="O263" t="inlineStr"/>
+      <c r="P263" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q263" t="n">
+        <v>6495.35</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -32854,6 +36136,12 @@
       </c>
       <c r="N264" t="inlineStr"/>
       <c r="O264" t="inlineStr"/>
+      <c r="P264" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q264" t="n">
+        <v>362.6</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -32917,6 +36205,12 @@
       </c>
       <c r="N265" t="inlineStr"/>
       <c r="O265" t="inlineStr"/>
+      <c r="P265" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q265" t="n">
+        <v>962</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -32980,6 +36274,12 @@
       </c>
       <c r="N266" t="inlineStr"/>
       <c r="O266" t="inlineStr"/>
+      <c r="P266" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q266" t="n">
+        <v>5170.75</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -33031,6 +36331,12 @@
       </c>
       <c r="N267" t="inlineStr"/>
       <c r="O267" t="inlineStr"/>
+      <c r="P267" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q267" t="n">
+        <v>6495.35</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -33094,6 +36400,12 @@
       </c>
       <c r="N268" t="inlineStr"/>
       <c r="O268" t="inlineStr"/>
+      <c r="P268" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q268" t="n">
+        <v>362.6</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -33157,6 +36469,12 @@
       </c>
       <c r="N269" t="inlineStr"/>
       <c r="O269" t="inlineStr"/>
+      <c r="P269" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q269" t="n">
+        <v>962</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -33220,6 +36538,12 @@
       </c>
       <c r="N270" t="inlineStr"/>
       <c r="O270" t="inlineStr"/>
+      <c r="P270" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q270" t="n">
+        <v>5170.75</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -33271,6 +36595,12 @@
       </c>
       <c r="N271" t="inlineStr"/>
       <c r="O271" t="inlineStr"/>
+      <c r="P271" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q271" t="n">
+        <v>6976.35</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -33334,6 +36664,12 @@
       </c>
       <c r="N272" t="inlineStr"/>
       <c r="O272" t="inlineStr"/>
+      <c r="P272" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q272" t="n">
+        <v>362.6</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -33397,6 +36733,12 @@
       </c>
       <c r="N273" t="inlineStr"/>
       <c r="O273" t="inlineStr"/>
+      <c r="P273" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q273" t="n">
+        <v>962</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -33460,6 +36802,12 @@
       </c>
       <c r="N274" t="inlineStr"/>
       <c r="O274" t="inlineStr"/>
+      <c r="P274" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q274" t="n">
+        <v>5651.75</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -33511,6 +36859,12 @@
       </c>
       <c r="N275" t="inlineStr"/>
       <c r="O275" t="inlineStr"/>
+      <c r="P275" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q275" t="n">
+        <v>5172.6</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -33574,6 +36928,12 @@
       </c>
       <c r="N276" t="inlineStr"/>
       <c r="O276" t="inlineStr"/>
+      <c r="P276" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q276" t="n">
+        <v>362.6</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -33637,6 +36997,12 @@
       </c>
       <c r="N277" t="inlineStr"/>
       <c r="O277" t="inlineStr"/>
+      <c r="P277" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q277" t="n">
+        <v>962</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -33700,6 +37066,12 @@
       </c>
       <c r="N278" t="inlineStr"/>
       <c r="O278" t="inlineStr"/>
+      <c r="P278" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q278" t="n">
+        <v>3848</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -33751,6 +37123,12 @@
       </c>
       <c r="N279" t="inlineStr"/>
       <c r="O279" t="inlineStr"/>
+      <c r="P279" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q279" t="n">
+        <v>6134.6</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -33814,6 +37192,12 @@
       </c>
       <c r="N280" t="inlineStr"/>
       <c r="O280" t="inlineStr"/>
+      <c r="P280" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q280" t="n">
+        <v>362.6</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -33877,6 +37261,12 @@
       </c>
       <c r="N281" t="inlineStr"/>
       <c r="O281" t="inlineStr"/>
+      <c r="P281" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q281" t="n">
+        <v>962</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -33940,6 +37330,12 @@
       </c>
       <c r="N282" t="inlineStr"/>
       <c r="O282" t="inlineStr"/>
+      <c r="P282" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q282" t="n">
+        <v>4810</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -33991,6 +37387,12 @@
       </c>
       <c r="N283" t="inlineStr"/>
       <c r="O283" t="inlineStr"/>
+      <c r="P283" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q283" t="n">
+        <v>4329</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -34054,6 +37456,12 @@
       </c>
       <c r="N284" t="inlineStr"/>
       <c r="O284" t="inlineStr"/>
+      <c r="P284" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q284" t="n">
+        <v>4329</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
